--- a/data/sentimen_berita.xlsx
+++ b/data/sentimen_berita.xlsx
@@ -253,7 +253,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="4320000"/>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4427,6 +4427,566 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>detikFinance - Berita Ekonomi Bisnis, dan Investasi Hari Ini</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>[Purbaya soal Efisiensi Anggaran MBG: Saya Maunya Nol, Tapi Nggak Bisa Kan](https://finance.detik.com/berita-ekonomi-bisnis/d-8549550/purbaya-soal-efisiensi-anggaran-mbg-saya-maunya-nol-tapi-nggak-bisa-kan)</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>[Trump Murka! AS Serang Iran Lagi](https://finance.detik.com/berita-ekonomi-bisnis/d-8549337/trump-murka-as-serang-iran-lagi)</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>[Terungkap Kondisi Pasokan Batu Bara PLN](https://finance.detik.com/energi/d-8549000/terungkap-kondisi-pasokan-batu-bara-pln)</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>[Duit Jumbo dari AIIB China yang Kata Purbaya Bukan Utang](https://finance.detik.com/berita-ekonomi-bisnis/d-8549025/duit-jumbo-dari-aiib-china-yang-kata-purbaya-bukan-utang)</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>[Rute MRT Lebak Bulus-Serpong Masih Rahasia demi Hindari Calo Tanah](https://finance.detik.com/infrastruktur/d-8549184/rute-mrt-lebak-bulus-serpong-masih-rahasia-demi-hindari-calo-tanah)</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>[Stok Batu Bara PLN Aman, ESDM Buka Lagi Keran Ekspor](https://finance.detik.com/energi/d-8549352/stok-batu-bara-pln-aman-esdm-buka-lagi-keran-ekspor)</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>POSITIF</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>[Ekspor Batu Bara Sempat Ditahan demi Pasokan ke PLN](https://finance.detik.com/energi/d-8548667/ekspor-batu-bara-sempat-ditahan-demi-pasokan-ke-pln)</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>[Beras IR. III (IR 64)](https://finance.detik.com/info-pangan/jakarta/beras-ir-iii-ir-64)</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>[Cabe Merah Keriting](https://finance.detik.com/info-pangan/jakarta/cabe-merah-keriting)</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>[Daging Sapi Murni (Semur)](https://finance.detik.com/info-pangan/jakarta/daging-sapi-murni-semur)</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>[Beli TV LED 50" UHD Smart di Transmart Full Day Sale Diskonnya Jutaan](https://finance.detik.com/berita-ekonomi-bisnis/d-8549706/beli-tv-led-50-uhd-smart-di-transmart-full-day-sale-diskonnya-jutaan)</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>POSITIF</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>[Puncak El Nino di Depan Mata, Pemerintah Pede Stok Beras Aman hingga Mei 2027](https://finance.detik.com/berita-ekonomi-bisnis/d-8549545/puncak-el-nino-di-depan-mata-pemerintah-pede-stok-beras-aman-hingga-mei-2027)</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>POSITIF</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>[Transmart Full Day Sale: Harga Sepeda Anak Cuma Rp 1 Jutaan!](https://finance.detik.com/berita-ekonomi-bisnis/d-8549696/transmart-full-day-sale-harga-sepeda-anak-cuma-rp-1-jutaan)</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>[Kemenperin Soroti Penyebab Implementasi Kebijakan HGBT Belum Optimal](https://finance.detik.com/industri/d-8550008/kemenperin-soroti-penyebab-implementasi-kebijakan-hgbt-belum-optimal)</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>Rekomendasi untuk Anda</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4438,7 +4998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4470,7 +5030,7 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
@@ -4485,11 +5045,11 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.6%</t>
         </is>
       </c>
     </row>
@@ -4504,7 +5064,7 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -4515,11 +5075,11 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>70.4%</t>
         </is>
       </c>
     </row>
@@ -4530,158 +5090,9 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>-0.112</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="C6" s="8" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Per Keyword</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Keyword</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>Positif</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>Negatif</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>Netral</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>Skor Avg</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>ekonomi indonesia</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>-0.013</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>harga pangan</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>inflasi indonesia</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>-0.125</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>rupiah dollar</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>ihsg bursa</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>-0.242</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/sentimen_berita.xlsx
+++ b/data/sentimen_berita.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4982,6 +4982,566 @@
         <v>0</v>
       </c>
       <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>detikFinance - Berita Ekonomi Bisnis, dan Investasi Hari Ini</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>[Purbaya soal Efisiensi Anggaran MBG: Saya Maunya Nol, Tapi Nggak Bisa Kan](https://finance.detik.com/berita-ekonomi-bisnis/d-8549550/purbaya-soal-efisiensi-anggaran-mbg-saya-maunya-nol-tapi-nggak-bisa-kan)</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>[Trump Murka! AS Serang Iran Lagi](https://finance.detik.com/berita-ekonomi-bisnis/d-8549337/trump-murka-as-serang-iran-lagi)</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>[Terungkap Kondisi Pasokan Batu Bara PLN](https://finance.detik.com/energi/d-8549000/terungkap-kondisi-pasokan-batu-bara-pln)</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>[Duit Jumbo dari AIIB China yang Kata Purbaya Bukan Utang](https://finance.detik.com/berita-ekonomi-bisnis/d-8549025/duit-jumbo-dari-aiib-china-yang-kata-purbaya-bukan-utang)</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>[Rute MRT Lebak Bulus-Serpong Masih Rahasia demi Hindari Calo Tanah](https://finance.detik.com/infrastruktur/d-8549184/rute-mrt-lebak-bulus-serpong-masih-rahasia-demi-hindari-calo-tanah)</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>[Stok Batu Bara PLN Aman, ESDM Buka Lagi Keran Ekspor](https://finance.detik.com/energi/d-8549352/stok-batu-bara-pln-aman-esdm-buka-lagi-keran-ekspor)</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>POSITIF</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>[Ekspor Batu Bara Sempat Ditahan demi Pasokan ke PLN](https://finance.detik.com/energi/d-8548667/ekspor-batu-bara-sempat-ditahan-demi-pasokan-ke-pln)</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>[Beras IR. III (IR 64)](https://finance.detik.com/info-pangan/jakarta/beras-ir-iii-ir-64)</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>[Cabe Merah Keriting](https://finance.detik.com/info-pangan/jakarta/cabe-merah-keriting)</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>[Daging Sapi Murni (Semur)](https://finance.detik.com/info-pangan/jakarta/daging-sapi-murni-semur)</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>[Beli TV LED 50" UHD Smart di Transmart Full Day Sale Diskonnya Jutaan](https://finance.detik.com/berita-ekonomi-bisnis/d-8549706/beli-tv-led-50-uhd-smart-di-transmart-full-day-sale-diskonnya-jutaan)</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>POSITIF</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>[Puncak El Nino di Depan Mata, Pemerintah Pede Stok Beras Aman hingga Mei 2027](https://finance.detik.com/berita-ekonomi-bisnis/d-8549545/puncak-el-nino-di-depan-mata-pemerintah-pede-stok-beras-aman-hingga-mei-2027)</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>POSITIF</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>[Transmart Full Day Sale: Harga Sepeda Anak Cuma Rp 1 Jutaan!](https://finance.detik.com/berita-ekonomi-bisnis/d-8549696/transmart-full-day-sale-harga-sepeda-anak-cuma-rp-1-jutaan)</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>[Kemenperin Soroti Penyebab Implementasi Kebijakan HGBT Belum Optimal](https://finance.detik.com/industri/d-8550008/kemenperin-soroti-penyebab-implementasi-kebijakan-hgbt-belum-optimal)</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>Rekomendasi untuk Anda</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>detik finance</t>
         </is>
@@ -5030,7 +5590,7 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
@@ -5045,11 +5605,11 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>10.6%</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5624,7 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>17.7%</t>
         </is>
       </c>
     </row>
@@ -5075,11 +5635,11 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>71.6%</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5650,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.062</v>
       </c>
       <c r="C6" s="8" t="inlineStr"/>
     </row>

--- a/data/sentimen_berita.xlsx
+++ b/data/sentimen_berita.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:G158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5542,6 +5542,566 @@
         <v>0</v>
       </c>
       <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>detikFinance - Berita Ekonomi Bisnis, dan Investasi Hari Ini</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>[Purbaya soal Efisiensi Anggaran MBG: Saya Maunya Nol, Tapi Nggak Bisa Kan](https://finance.detik.com/berita-ekonomi-bisnis/d-8549550/purbaya-soal-efisiensi-anggaran-mbg-saya-maunya-nol-tapi-nggak-bisa-kan)</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>[Trump Murka! AS Serang Iran Lagi](https://finance.detik.com/berita-ekonomi-bisnis/d-8549337/trump-murka-as-serang-iran-lagi)</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>[Terungkap Kondisi Pasokan Batu Bara PLN](https://finance.detik.com/energi/d-8549000/terungkap-kondisi-pasokan-batu-bara-pln)</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>[Duit Jumbo dari AIIB China yang Kata Purbaya Bukan Utang](https://finance.detik.com/berita-ekonomi-bisnis/d-8549025/duit-jumbo-dari-aiib-china-yang-kata-purbaya-bukan-utang)</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>[Rute MRT Lebak Bulus-Serpong Masih Rahasia demi Hindari Calo Tanah](https://finance.detik.com/infrastruktur/d-8549184/rute-mrt-lebak-bulus-serpong-masih-rahasia-demi-hindari-calo-tanah)</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>[Dilanda Panas Ekstrem, Warga Eropa Panic Buying Rebutan AC](https://finance.detik.com/berita-ekonomi-bisnis/d-8550247/dilanda-panas-ekstrem-warga-eropa-panic-buying-rebutan-ac)</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F149" s="6" t="n">
+        <v>-0.511</v>
+      </c>
+      <c r="G149" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>[Harga Beras di Jepang Akhirnya Turun Setelah 3,5 Tahun](https://finance.detik.com/berita-ekonomi-bisnis/d-8539811/harga-beras-di-jepang-akhirnya-turun-setelah-3-5-tahun)</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F150" s="6" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G150" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>[Trump Ancam Naikkan Tarif Impor Mobil Eropa Jadi 25%](https://finance.detik.com/berita-ekonomi-bisnis/d-8471046/trump-ancam-naikkan-tarif-impor-mobil-eropa-jadi-25)</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>POSITIF</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G151" s="4" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>[Beras IR. III (IR 64)](https://finance.detik.com/info-pangan/jakarta/beras-ir-iii-ir-64)</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>[Cabe Merah Keriting](https://finance.detik.com/info-pangan/jakarta/cabe-merah-keriting)</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>[Daging Sapi Murni (Semur)](https://finance.detik.com/info-pangan/jakarta/daging-sapi-murni-semur)</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>[Terungkap Biang Kerok AS Serang Iran Lagi](https://finance.detik.com/berita-ekonomi-bisnis/d-8550246/terungkap-biang-kerok-as-serang-iran-lagi)</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>[Kisah Penyintas Kanker Ekspor Kain Botanical Print ke Prancis-Brazil](https://finance.detik.com/solusiukm/d-8550302/kisah-penyintas-kanker-ekspor-kain-botanical-print-ke-prancis-brazil)</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>[Usaha Camilan Sehat Malika Tembus Ritel Modern hingga Apotek](https://finance.detik.com/solusiukm/d-8550237/usaha-camilan-sehat-malika-tembus-ritel-modern-hingga-apotek)</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D158" s="7" t="inlineStr">
+        <is>
+          <t>[Waduh! Produsen Mobil VW Mau PHK 100.000 Karyawan &amp; Tutup 4 Pabrik](https://finance.detik.com/berita-ekonomi-bisnis/d-8549367/waduh-produsen-mobil-vw-mau-phk-100-000-karyawan-tutup-4-pabrik)</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F158" s="6" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G158" s="6" t="inlineStr">
         <is>
           <t>detik finance</t>
         </is>
@@ -5590,7 +6150,7 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
@@ -5605,11 +6165,11 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.2%</t>
         </is>
       </c>
     </row>
@@ -5620,11 +6180,11 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.8%</t>
         </is>
       </c>
     </row>
@@ -5635,11 +6195,11 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>72.0%</t>
         </is>
       </c>
     </row>
@@ -5650,7 +6210,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>-0.062</v>
+        <v>-0.063</v>
       </c>
       <c r="C6" s="8" t="inlineStr"/>
     </row>

--- a/data/sentimen_berita.xlsx
+++ b/data/sentimen_berita.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G158"/>
+  <dimension ref="A1:G174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6102,6 +6102,566 @@
         <v>-0.65</v>
       </c>
       <c r="G158" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>detikFinance - Berita Ekonomi Bisnis, dan Investasi Hari Ini</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D160" s="7" t="inlineStr">
+        <is>
+          <t>[Harga Emas Antam Turun dalam Sepekan, Buyback Anjlok Rp 20 Ribu/Gram](https://finance.detik.com/berita-ekonomi-bisnis/d-8550494/harga-emas-antam-turun-dalam-sepekan-buyback-anjlok-rp-20-ribu-gram)</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D161" s="7" t="inlineStr">
+        <is>
+          <t>[Harga Ayam di Pasar Ikut Anjlok Jadi Rp 35.000/Kg, Ini Biang Keroknya](https://finance.detik.com/berita-ekonomi-bisnis/d-8550248/harga-ayam-di-pasar-ikut-anjlok-jadi-rp-35-000-kg-ini-biang-keroknya)</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G161" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D162" s="7" t="inlineStr">
+        <is>
+          <t>[Dilanda Panas Ekstrem, Warga Eropa Panic Buying Rebutan AC](https://finance.detik.com/berita-ekonomi-bisnis/d-8550247/dilanda-panas-ekstrem-warga-eropa-panic-buying-rebutan-ac)</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="n">
+        <v>-0.511</v>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>[Terungkap Biang Kerok AS Serang Iran Lagi](https://finance.detik.com/berita-ekonomi-bisnis/d-8550246/terungkap-biang-kerok-as-serang-iran-lagi)</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>[Purbaya soal Efisiensi Anggaran MBG: Saya Maunya Nol, Tapi Nggak Bisa Kan](https://finance.detik.com/berita-ekonomi-bisnis/d-8549550/purbaya-soal-efisiensi-anggaran-mbg-saya-maunya-nol-tapi-nggak-bisa-kan)</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>[Prabowo Singgung Swasta Ikut Nikmati Susbidi Listrik-BBM](https://finance.detik.com/berita-ekonomi-bisnis/d-8550638/prabowo-singgung-swasta-ikut-nikmati-susbidi-listrik-bbm)</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>[Dapat Usulan Untung BUMN buat Biaya Riset, Prabowo: Masalahnya Ada Laba Nggak?](https://finance.detik.com/berita-ekonomi-bisnis/d-8550603/dapat-usulan-untung-bumn-buat-biaya-riset-prabowo-masalahnya-ada-laba-nggak)</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>[Prabowo Singgung soal Gaduh-gaduh: Kapan Rakyat Sejahtera?](https://finance.detik.com/berita-ekonomi-bisnis/d-8548940/prabowo-singgung-soal-gaduh-gaduh-kapan-rakyat-sejahtera)</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>POSITIF</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>[Beras IR. III (IR 64)](https://finance.detik.com/info-pangan/jakarta/beras-ir-iii-ir-64)</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>[Cabe Merah Keriting](https://finance.detik.com/info-pangan/jakarta/cabe-merah-keriting)</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>[Daging Sapi Murni (Semur)](https://finance.detik.com/info-pangan/jakarta/daging-sapi-murni-semur)</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>[DJP Tunjuk 7 Pemungut Pajak Digital Baru, Ada Strava](https://finance.detik.com/berita-ekonomi-bisnis/d-8550575/djp-tunjuk-7-pemungut-pajak-digital-baru-ada-strava)</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>[Alat Makan &amp; Minum Diskon Gede-gedean di Transmart Full Day Sale](https://finance.detik.com/berita-ekonomi-bisnis/d-8550477/alat-makan-minum-diskon-gede-gedean-di-transmart-full-day-sale)</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>[Pemerintah Kantongi Rp 52,85 T dari Pajak Kripto-Pinjol, Ini Rinciannya](https://finance.detik.com/berita-ekonomi-bisnis/d-8550537/pemerintah-kantongi-rp-52-85-t-dari-pajak-kripto-pinjol-ini-rinciannya)</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>Rekomendasi untuk Anda</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t>detik finance</t>
         </is>
@@ -6150,7 +6710,7 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
@@ -6165,11 +6725,11 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>9.8%</t>
         </is>
       </c>
     </row>
@@ -6180,11 +6740,11 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.9%</t>
         </is>
       </c>
     </row>
@@ -6195,11 +6755,11 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>72.3%</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6770,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>-0.063</v>
+        <v>-0.065</v>
       </c>
       <c r="C6" s="8" t="inlineStr"/>
     </row>

--- a/data/sentimen_berita.xlsx
+++ b/data/sentimen_berita.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G174"/>
+  <dimension ref="A1:G190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6662,6 +6662,566 @@
         <v>0</v>
       </c>
       <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>detikFinance - Berita Ekonomi Bisnis, dan Investasi Hari Ini</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D176" s="7" t="inlineStr">
+        <is>
+          <t>[Harga Emas Antam Turun dalam Sepekan, Buyback Anjlok Rp 20 Ribu/Gram](https://finance.detik.com/berita-ekonomi-bisnis/d-8550494/harga-emas-antam-turun-dalam-sepekan-buyback-anjlok-rp-20-ribu-gram)</t>
+        </is>
+      </c>
+      <c r="E176" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F176" s="6" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="G176" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B177" s="6" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="C177" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D177" s="7" t="inlineStr">
+        <is>
+          <t>[Harga Ayam di Pasar Ikut Anjlok Jadi Rp 35.000/Kg, Ini Biang Keroknya](https://finance.detik.com/berita-ekonomi-bisnis/d-8550248/harga-ayam-di-pasar-ikut-anjlok-jadi-rp-35-000-kg-ini-biang-keroknya)</t>
+        </is>
+      </c>
+      <c r="E177" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F177" s="6" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G177" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B178" s="6" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D178" s="7" t="inlineStr">
+        <is>
+          <t>[Dilanda Panas Ekstrem, Warga Eropa Panic Buying Rebutan AC](https://finance.detik.com/berita-ekonomi-bisnis/d-8550247/dilanda-panas-ekstrem-warga-eropa-panic-buying-rebutan-ac)</t>
+        </is>
+      </c>
+      <c r="E178" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F178" s="6" t="n">
+        <v>-0.511</v>
+      </c>
+      <c r="G178" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>[Terungkap Biang Kerok AS Serang Iran Lagi](https://finance.detik.com/berita-ekonomi-bisnis/d-8550246/terungkap-biang-kerok-as-serang-iran-lagi)</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>[Purbaya soal Efisiensi Anggaran MBG: Saya Maunya Nol, Tapi Nggak Bisa Kan](https://finance.detik.com/berita-ekonomi-bisnis/d-8549550/purbaya-soal-efisiensi-anggaran-mbg-saya-maunya-nol-tapi-nggak-bisa-kan)</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>[Prabowo Singgung Swasta Ikut Nikmati Susbidi Listrik-BBM](https://finance.detik.com/berita-ekonomi-bisnis/d-8550638/prabowo-singgung-swasta-ikut-nikmati-susbidi-listrik-bbm)</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>[Dapat Usulan Untung BUMN buat Biaya Riset, Prabowo: Masalahnya Ada Laba Nggak?](https://finance.detik.com/berita-ekonomi-bisnis/d-8550603/dapat-usulan-untung-bumn-buat-biaya-riset-prabowo-masalahnya-ada-laba-nggak)</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>[Prabowo Singgung soal Gaduh-gaduh: Kapan Rakyat Sejahtera?](https://finance.detik.com/berita-ekonomi-bisnis/d-8548940/prabowo-singgung-soal-gaduh-gaduh-kapan-rakyat-sejahtera)</t>
+        </is>
+      </c>
+      <c r="E183" s="4" t="inlineStr">
+        <is>
+          <t>POSITIF</t>
+        </is>
+      </c>
+      <c r="F183" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G183" s="4" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>[Beras IR. III (IR 64)](https://finance.detik.com/info-pangan/jakarta/beras-ir-iii-ir-64)</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>[Cabe Merah Keriting](https://finance.detik.com/info-pangan/jakarta/cabe-merah-keriting)</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>[Daging Sapi Murni (Semur)](https://finance.detik.com/info-pangan/jakarta/daging-sapi-murni-semur)</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>[DJP Tunjuk 7 Pemungut Pajak Digital Baru, Ada Strava](https://finance.detik.com/berita-ekonomi-bisnis/d-8550575/djp-tunjuk-7-pemungut-pajak-digital-baru-ada-strava)</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>[Pemerintah Kantongi Rp 52,85 T dari Pajak Kripto-Pinjol, Ini Rinciannya](https://finance.detik.com/berita-ekonomi-bisnis/d-8550537/pemerintah-kantongi-rp-52-85-t-dari-pajak-kripto-pinjol-ini-rinciannya)</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>[Rak Besi Banting Harga di Transmart Full Day Sale, Serbu!](https://finance.detik.com/berita-ekonomi-bisnis/d-8550451/rak-besi-banting-harga-di-transmart-full-day-sale-serbu)</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>[PLTP Dieng Unit 2 Mulai Dibangun, Segini Kapasitasnya](https://finance.detik.com/energi/d-8550378/pltp-dieng-unit-2-mulai-dibangun-segini-kapasitasnya)</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
         <is>
           <t>detik finance</t>
         </is>
@@ -6710,7 +7270,7 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
@@ -6725,11 +7285,11 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.5%</t>
         </is>
       </c>
     </row>
@@ -6740,11 +7300,11 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.0%</t>
         </is>
       </c>
     </row>
@@ -6755,11 +7315,11 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.5%</t>
         </is>
       </c>
     </row>
@@ -6770,7 +7330,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>-0.065</v>
+        <v>-0.067</v>
       </c>
       <c r="C6" s="8" t="inlineStr"/>
     </row>

--- a/data/sentimen_berita.xlsx
+++ b/data/sentimen_berita.xlsx
@@ -191,6 +191,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -562,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G259"/>
+  <dimension ref="A1:G318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9636,6 +9637,2071 @@
         <v>0.65</v>
       </c>
       <c r="G259" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>detikFinance - Berita Ekonomi Bisnis, dan Investasi Hari Ini</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F260" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>[Prabowo: Tak Ada Pertumbuhan Ekonomi Tanpa Kepastian Hukum](https://finance.detik.com/berita-ekonomi-bisnis/d-8554797/prabowo-tak-ada-pertumbuhan-ekonomi-tanpa-kepastian-hukum)</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>POSITIF</t>
+        </is>
+      </c>
+      <c r="F261" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>[Bandara Husein Sastranegara Ditargetkan Beroperasi Lagi 17 September](https://finance.detik.com/berita-ekonomi-bisnis/d-8554712/bandara-husein-sastranegara-ditargetkan-beroperasi-lagi-17-september)</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F262" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>[Harga BBM Diesel Shell &amp; BP Turun, Ini Daftarnya](https://finance.detik.com/energi/d-8554652/harga-bbm-diesel-shell-bp-turun-ini-daftarnya)</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F263" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>[Pertamax Tetap! Ini Daftar BBM Pertamina yang Turun Harga](https://finance.detik.com/energi/d-8554611/pertamax-tetap-ini-daftar-bbm-pertamina-yang-turun-harga)</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F264" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>[Harga Pertamax Turbo hingga Avtur Turun Mulai 1 Juli](https://finance.detik.com/energi/d-8554607/harga-pertamax-turbo-hingga-avtur-turun-mulai-1-juli)</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F265" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>[Prabowo: Rakyat Menderita Kemiskinan Akibat Kegiatan Ekonomi Ilegal!](https://finance.detik.com/berita-ekonomi-bisnis/d-8554818/prabowo-rakyat-menderita-kemiskinan-akibat-kegiatan-ekonomi-ilegal)</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F266" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>[Prabowo Pangkas Gede-gedean BUMN, dari 1.000 Sisa 250 Tahun Ini](https://finance.detik.com/berita-ekonomi-bisnis/d-8551319/prabowo-pangkas-gede-gedean-bumn-dari-1-000-sisa-250-tahun-ini)</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F267" t="n">
+        <v>0</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>[Beras IR. III (IR 64)](https://finance.detik.com/info-pangan/jakarta/beras-ir-iii-ir-64)</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F268" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>[Cabe Merah Keriting](https://finance.detik.com/info-pangan/jakarta/cabe-merah-keriting)</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F269" t="n">
+        <v>0</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>[Daging Sapi Murni (Semur)](https://finance.detik.com/info-pangan/jakarta/daging-sapi-murni-semur)</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F270" t="n">
+        <v>0</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>[Dolar AS Kembali Tekan Rupiah Dekati Rp 18.000](https://finance.detik.com/bursa-dan-valas/d-8554784/dolar-as-kembali-tekan-rupiah-dekati-rp-18-000)</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F271" t="n">
+        <v>0</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>[IHSG Dibuka Dua Arah, Mentok di Level 5.700](https://finance.detik.com/bursa-dan-valas/d-8554781/ihsg-dibuka-dua-arah-mentok-di-level-5-700)</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>[Jaringan Irigasi Air Tanah Bantu Petani Jaga Pasokan Air Sawah](https://finance.detik.com/foto-bisnis/d-8554146/jaringan-irigasi-air-tanah-bantu-petani-jaga-pasokan-air-sawah)</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>[Pupuk Kaltim Raih Penghargaan AREA, Bukti Upaya Bangun Ekonomi Inklusif](https://finance.detik.com/industri/d-8554706/pupuk-kaltim-raih-penghargaan-area-bukti-upaya-bangun-ekonomi-inklusif)</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>[Kripto hingga Saham Jadi Sumber Duit Trump, Nilainya Fantastis!](https://finance.detik.com/berita-ekonomi-bisnis/d-8554701/kripto-hingga-saham-jadi-sumber-duit-trump-nilainya-fantastis)</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>[Prabowo: Jadilah Polisi Dekat Rakyat, Gaji Kita dari Rakyat](https://finance.detik.com/berita-ekonomi-bisnis/d-8554838/prabowo-jadilah-polisi-dekat-rakyat-gaji-kita-dari-rakyat)</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>[Dana Kelolaan Investasi INA Tembus Rp 146 Triliun](https://finance.detik.com/berita-ekonomi-bisnis/d-8555051/dana-kelolaan-investasi-ina-tembus-rp-146-triliun)</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>[Direktur Pegadaian Beberkan Strategi Kelola Keuangan ke Mahasiswa Andalas](https://finance.detik.com/berita-ekonomi-bisnis/d-8554182/direktur-pegadaian-beberkan-strategi-kelola-keuangan-ke-mahasiswa-andalas)</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>[Surplus Dagang RI 72 Bulan Beruntun Tamat! Kini Defisit US$ 1,61 Miliar](https://finance.detik.com/berita-ekonomi-bisnis/d-8555050/surplus-dagang-ri-72-bulan-beruntun-tamat-kini-defisit-us-1-61-miliar)</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>[RI Makin Banyak Impor, Meroket 22% di Mei 2026](https://finance.detik.com/berita-ekonomi-bisnis/d-8555038/ri-makin-banyak-impor-meroket-22-di-mei-2026)</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>[4 Toko Online Bakal Pungut Pajak Seller, Ini Daftarnya](https://finance.detik.com/berita-ekonomi-bisnis/d-8555006/4-toko-online-bakal-pungut-pajak-seller-ini-daftarnya)</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>[Ekspor RI Mei 2026 Turun 5,73%, Anjlok karena Perhiasan hingga Besi Baja](https://finance.detik.com/berita-ekonomi-bisnis/d-8555003/ekspor-ri-mei-2026-turun-5-73-anjlok-karena-perhiasan-hingga-besi-baja)</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F282" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>[BPS: Juni 2026 Inflasi 0,44%, Dipicu Harga Bensin hingga Tarif Pesawat](https://finance.detik.com/berita-ekonomi-bisnis/d-8554951/bps-juni-2026-inflasi-0-44-dipicu-harga-bensin-hingga-tarif-pesawat)</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F283" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>[Harga Batu Bara Acuan Juli Naik!](https://finance.detik.com/energi/d-8555183/harga-batu-bara-acuan-juli-naik)</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>POSITIF</t>
+        </is>
+      </c>
+      <c r="F284" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>[B50 Mulai Berlaku Hari Ini, Diresmikan Prabowo Awal Juli](https://finance.detik.com/energi/d-8554850/b50-mulai-berlaku-hari-ini-diresmikan-prabowo-awal-juli)</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F285" t="n">
+        <v>0</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>[Tarif Listrik Juli-Agustus-September Nggak Naik!](https://finance.detik.com/energi/d-8554420/tarif-listrik-juli-agustus-september-nggak-naik)</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>POSITIF</t>
+        </is>
+      </c>
+      <c r="F286" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>[Bina Marga Minta Tambahan Anggaran Rp 54 T, Pagu Dipangkas Nyaris 40%](https://finance.detik.com/infrastruktur/d-8555176/bina-marga-minta-tambahan-anggaran-rp-54-t-pagu-dipangkas-nyaris-40)</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F287" t="n">
+        <v>0</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>[Buruh Minta Pajak JHT Dihapus, Bos DJP: Sedang Dikaji](https://finance.detik.com/berita-ekonomi-bisnis/d-8555157/buruh-minta-pajak-jht-dihapus-bos-djp-sedang-dikaji)</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F288" t="n">
+        <v>0</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>[Polri Ikut Kawal Isu PHK, 4.200 Buruh Bisa Kerja Lagi](https://finance.detik.com/berita-ekonomi-bisnis/d-8555158/polri-ikut-kawal-isu-phk-4-200-buruh-bisa-kerja-lagi)</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F289" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>[BPKH Pangkas Biaya Operasional Rp 100 M](https://finance.detik.com/berita-ekonomi-bisnis/d-8555145/bpkh-pangkas-biaya-operasional-rp-100-m)</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F290" t="n">
+        <v>0</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>[Kesejahteraan Petani di RI Turun, Padahal Harga Beras Naik](https://finance.detik.com/berita-ekonomi-bisnis/d-8555364/kesejahteraan-petani-di-ri-turun-padahal-harga-beras-naik)</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>POSITIF</t>
+        </is>
+      </c>
+      <c r="F291" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>[Harga Cabai Rawit Masih Pedas di Rp 76.000/Kg](https://finance.detik.com/berita-ekonomi-bisnis/d-8541311/harga-cabai-rawit-masih-pedas-di-rp-76-000-kg)</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F292" t="n">
+        <v>0</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>[Data FAO: RI Produsen Beras Terbesar di ASEAN dan Nomor 4 Dunia](https://finance.detik.com/berita-ekonomi-bisnis/d-8539866/data-fao-ri-produsen-beras-terbesar-di-asean-dan-nomor-4-dunia)</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F293" t="n">
+        <v>0</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>[PNS di Malaysia Boleh WFH 2 Hari Seminggu, Mulai Berlaku Agustus](https://finance.detik.com/berita-ekonomi-bisnis/d-8555341/pns-di-malaysia-boleh-wfh-2-hari-seminggu-mulai-berlaku-agustus)</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F294" t="n">
+        <v>0</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>[Sudah Ada 6 Juta Turis Asing yang Datangi RI, Paling Banyak ke Bali](https://finance.detik.com/berita-ekonomi-bisnis/d-8555250/sudah-ada-6-juta-turis-asing-yang-datangi-ri-paling-banyak-ke-bali)</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F295" t="n">
+        <v>0</v>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>[DJP Sederhanakan Tampilan Coretax](https://finance.detik.com/berita-ekonomi-bisnis/d-8555236/djp-sederhanakan-tampilan-coretax)</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F296" t="n">
+        <v>0</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>[Mitratel Sebar 98% Laba Bersih Jadi Dividen Rp 2,08 T](https://finance.detik.com/bursa-dan-valas/d-8555213/mitratel-sebar-98-laba-bersih-jadi-dividen-rp-2-08-t)</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F297" t="n">
+        <v>0</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>[Tak Terbendung! Impor Barang China Banjiri RI, Capai US$ 39 Miliar](https://finance.detik.com/berita-ekonomi-bisnis/d-8555459/tak-terbendung-impor-barang-china-banjiri-ri-capai-us-39-miliar)</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F298" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>[Kabar Buat Pengendara! Tol Japek II Selatan Ditargetkan Selesai 2027](https://finance.detik.com/infrastruktur/d-8555436/kabar-buat-pengendara-tol-japek-ii-selatan-ditargetkan-selesai-2027)</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F299" t="n">
+        <v>0</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>[Driver Ojol Bakal Masuk Kategori UMKM, Penghasilan Bebas Pajak](https://finance.detik.com/berita-ekonomi-bisnis/d-8555416/driver-ojol-bakal-masuk-kategori-umkm-penghasilan-bebas-pajak)</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F300" t="n">
+        <v>0</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>[RI Butuh Investasi Rp 14.369 T buat Geber Ekonomi 8%](https://finance.detik.com/berita-ekonomi-bisnis/d-8555398/ri-butuh-investasi-rp-14-369-t-buat-geber-ekonomi-8)</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F301" t="n">
+        <v>0</v>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>[PMI Manufaktur RI Masuk Zona Merah, Kemenperin Ungkap Penyebabnya](https://finance.detik.com/industri/d-8555392/pmi-manufaktur-ri-masuk-zona-merah-kemenperin-ungkap-penyebabnya)</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F302" t="n">
+        <v>0</v>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D303" s="3" t="inlineStr">
+        <is>
+          <t>detikFinance - Berita Ekonomi Bisnis, dan Investasi Hari Ini</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D304" s="3" t="inlineStr">
+        <is>
+          <t>[Prabowo: Jadilah Polisi Dekat Rakyat, Gaji Kita dari Rakyat](https://finance.detik.com/berita-ekonomi-bisnis/d-8554838/prabowo-jadilah-polisi-dekat-rakyat-gaji-kita-dari-rakyat)</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B305" s="4" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C305" s="4" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D305" s="5" t="inlineStr">
+        <is>
+          <t>[Prabowo: Tak Ada Pertumbuhan Ekonomi Tanpa Kepastian Hukum](https://finance.detik.com/berita-ekonomi-bisnis/d-8554797/prabowo-tak-ada-pertumbuhan-ekonomi-tanpa-kepastian-hukum)</t>
+        </is>
+      </c>
+      <c r="E305" s="4" t="inlineStr">
+        <is>
+          <t>POSITIF</t>
+        </is>
+      </c>
+      <c r="F305" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G305" s="4" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D306" s="3" t="inlineStr">
+        <is>
+          <t>[Bandara Husein Sastranegara Ditargetkan Beroperasi Lagi 17 September](https://finance.detik.com/berita-ekonomi-bisnis/d-8554712/bandara-husein-sastranegara-ditargetkan-beroperasi-lagi-17-september)</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B307" s="6" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C307" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D307" s="7" t="inlineStr">
+        <is>
+          <t>[Harga BBM Diesel Shell &amp; BP Turun, Ini Daftarnya](https://finance.detik.com/energi/d-8554652/harga-bbm-diesel-shell-bp-turun-ini-daftarnya)</t>
+        </is>
+      </c>
+      <c r="E307" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F307" s="6" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G307" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B308" s="6" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C308" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D308" s="7" t="inlineStr">
+        <is>
+          <t>[Pertamax Tetap! Ini Daftar BBM Pertamina yang Turun Harga](https://finance.detik.com/energi/d-8554611/pertamax-tetap-ini-daftar-bbm-pertamina-yang-turun-harga)</t>
+        </is>
+      </c>
+      <c r="E308" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F308" s="6" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G308" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D309" s="3" t="inlineStr">
+        <is>
+          <t>[Drone Buatan Bandung Tembus Pasar Australia dan Korea](https://finance.detik.com/foto-bisnis/d-8555166/drone-buatan-bandung-tembus-pasar-australia-dan-korea)</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D310" s="3" t="inlineStr">
+        <is>
+          <t>[Beras IR. III (IR 64)](https://finance.detik.com/info-pangan/jakarta/beras-ir-iii-ir-64)</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D311" s="3" t="inlineStr">
+        <is>
+          <t>[Cabe Merah Keriting](https://finance.detik.com/info-pangan/jakarta/cabe-merah-keriting)</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D312" s="3" t="inlineStr">
+        <is>
+          <t>[Daging Sapi Murni (Semur)](https://finance.detik.com/info-pangan/jakarta/daging-sapi-murni-semur)</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D313" s="3" t="inlineStr">
+        <is>
+          <t>[Alasan INA Masih Genggam Saham Bank BUMN Saat Pasar Gonjang-ganjing](https://finance.detik.com/bursa-dan-valas/d-8555623/alasan-ina-masih-genggam-saham-bank-bumn-saat-pasar-gonjang-ganjing)</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="inlineStr">
+        <is>
+          <t>[Toko Online Pungut Pajak Mulai Agustus, Sistem Sudah Siap?](https://finance.detik.com/berita-ekonomi-bisnis/d-8555604/toko-online-pungut-pajak-mulai-agustus-sistem-sudah-siap)</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B315" s="6" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C315" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D315" s="7" t="inlineStr">
+        <is>
+          <t>[IHSG Ditutup Menguat Tipis ke 5.695](https://finance.detik.com/bursa-dan-valas/d-8555582/ihsg-ditutup-menguat-tipis-ke-5-695)</t>
+        </is>
+      </c>
+      <c r="E315" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F315" s="6" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G315" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>[Impor Migas RI Makin Bengkak, Paling Banyak dari Singapura](https://finance.detik.com/energi/d-8555589/impor-migas-ri-makin-bengkak-paling-banyak-dari-singapura)</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D317" s="3" t="inlineStr">
+        <is>
+          <t>[DJP Buka Peluang Tambah Toko Online Pungut Pajak](https://finance.detik.com/berita-ekonomi-bisnis/d-8555569/djp-buka-peluang-tambah-toko-online-pungut-pajak)</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D318" s="3" t="inlineStr">
+        <is>
+          <t>[Harta Trump Melejit Rp 75 Triliun Sejak Jadi Presiden AS Lagi](https://finance.detik.com/berita-ekonomi-bisnis/d-8555547/harta-trump-melejit-rp-75-triliun-sejak-jadi-presiden-as-lagi)</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G318" s="2" t="inlineStr">
         <is>
           <t>detik finance</t>
         </is>
@@ -9684,7 +11750,7 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
@@ -9699,11 +11765,11 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.1%</t>
         </is>
       </c>
     </row>
@@ -9714,11 +11780,11 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>19.6%</t>
         </is>
       </c>
     </row>
@@ -9729,11 +11795,11 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>70.3%</t>
         </is>
       </c>
     </row>
@@ -9744,7 +11810,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>-0.062</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="C6" s="8" t="inlineStr"/>
     </row>

--- a/data/sentimen_berita.xlsx
+++ b/data/sentimen_berita.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G318"/>
+  <dimension ref="A1:G357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -11148,245 +11148,245 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="inlineStr">
+      <c r="A303" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="B303" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="C303" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D303" s="3" t="inlineStr">
-        <is>
-          <t>detikFinance - Berita Ekonomi Bisnis, dan Investasi Hari Ini</t>
-        </is>
-      </c>
-      <c r="E303" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F303" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G303" s="2" t="inlineStr">
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>[Drone Buatan Bandung Tembus Pasar Australia dan Korea](https://finance.detik.com/foto-bisnis/d-8555166/drone-buatan-bandung-tembus-pasar-australia-dan-korea)</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F303" t="n">
+        <v>0</v>
+      </c>
+      <c r="G303" t="inlineStr">
         <is>
           <t>detik finance</t>
         </is>
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="inlineStr">
+      <c r="A304" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="B304" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="C304" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D304" s="3" t="inlineStr">
-        <is>
-          <t>[Prabowo: Jadilah Polisi Dekat Rakyat, Gaji Kita dari Rakyat](https://finance.detik.com/berita-ekonomi-bisnis/d-8554838/prabowo-jadilah-polisi-dekat-rakyat-gaji-kita-dari-rakyat)</t>
-        </is>
-      </c>
-      <c r="E304" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F304" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G304" s="2" t="inlineStr">
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>[Alasan INA Masih Genggam Saham Bank BUMN Saat Pasar Gonjang-ganjing](https://finance.detik.com/bursa-dan-valas/d-8555623/alasan-ina-masih-genggam-saham-bank-bumn-saat-pasar-gonjang-ganjing)</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F304" t="n">
+        <v>0</v>
+      </c>
+      <c r="G304" t="inlineStr">
         <is>
           <t>detik finance</t>
         </is>
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="4" t="inlineStr">
+      <c r="A305" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="B305" s="4" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="C305" s="4" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D305" s="5" t="inlineStr">
-        <is>
-          <t>[Prabowo: Tak Ada Pertumbuhan Ekonomi Tanpa Kepastian Hukum](https://finance.detik.com/berita-ekonomi-bisnis/d-8554797/prabowo-tak-ada-pertumbuhan-ekonomi-tanpa-kepastian-hukum)</t>
-        </is>
-      </c>
-      <c r="E305" s="4" t="inlineStr">
-        <is>
-          <t>POSITIF</t>
-        </is>
-      </c>
-      <c r="F305" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G305" s="4" t="inlineStr">
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>[Toko Online Pungut Pajak Mulai Agustus, Sistem Sudah Siap?](https://finance.detik.com/berita-ekonomi-bisnis/d-8555604/toko-online-pungut-pajak-mulai-agustus-sistem-sudah-siap)</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F305" t="n">
+        <v>0</v>
+      </c>
+      <c r="G305" t="inlineStr">
         <is>
           <t>detik finance</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="inlineStr">
+      <c r="A306" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="B306" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="C306" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D306" s="3" t="inlineStr">
-        <is>
-          <t>[Bandara Husein Sastranegara Ditargetkan Beroperasi Lagi 17 September](https://finance.detik.com/berita-ekonomi-bisnis/d-8554712/bandara-husein-sastranegara-ditargetkan-beroperasi-lagi-17-september)</t>
-        </is>
-      </c>
-      <c r="E306" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F306" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G306" s="2" t="inlineStr">
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>[IHSG Ditutup Menguat Tipis ke 5.695](https://finance.detik.com/bursa-dan-valas/d-8555582/ihsg-ditutup-menguat-tipis-ke-5-695)</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F306" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G306" t="inlineStr">
         <is>
           <t>detik finance</t>
         </is>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="6" t="inlineStr">
+      <c r="A307" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="B307" s="6" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="C307" s="6" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D307" s="7" t="inlineStr">
-        <is>
-          <t>[Harga BBM Diesel Shell &amp; BP Turun, Ini Daftarnya](https://finance.detik.com/energi/d-8554652/harga-bbm-diesel-shell-bp-turun-ini-daftarnya)</t>
-        </is>
-      </c>
-      <c r="E307" s="6" t="inlineStr">
-        <is>
-          <t>NEGATIF</t>
-        </is>
-      </c>
-      <c r="F307" s="6" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="G307" s="6" t="inlineStr">
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>[Impor Migas RI Makin Bengkak, Paling Banyak dari Singapura](https://finance.detik.com/energi/d-8555589/impor-migas-ri-makin-bengkak-paling-banyak-dari-singapura)</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F307" t="n">
+        <v>0</v>
+      </c>
+      <c r="G307" t="inlineStr">
         <is>
           <t>detik finance</t>
         </is>
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="6" t="inlineStr">
+      <c r="A308" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="B308" s="6" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="C308" s="6" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D308" s="7" t="inlineStr">
-        <is>
-          <t>[Pertamax Tetap! Ini Daftar BBM Pertamina yang Turun Harga](https://finance.detik.com/energi/d-8554611/pertamax-tetap-ini-daftar-bbm-pertamina-yang-turun-harga)</t>
-        </is>
-      </c>
-      <c r="E308" s="6" t="inlineStr">
-        <is>
-          <t>NEGATIF</t>
-        </is>
-      </c>
-      <c r="F308" s="6" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="G308" s="6" t="inlineStr">
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>[DJP Buka Peluang Tambah Toko Online Pungut Pajak](https://finance.detik.com/berita-ekonomi-bisnis/d-8555569/djp-buka-peluang-tambah-toko-online-pungut-pajak)</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F308" t="n">
+        <v>0</v>
+      </c>
+      <c r="G308" t="inlineStr">
         <is>
           <t>detik finance</t>
         </is>
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="inlineStr">
+      <c r="A309" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="B309" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="C309" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D309" s="3" t="inlineStr">
-        <is>
-          <t>[Drone Buatan Bandung Tembus Pasar Australia dan Korea](https://finance.detik.com/foto-bisnis/d-8555166/drone-buatan-bandung-tembus-pasar-australia-dan-korea)</t>
-        </is>
-      </c>
-      <c r="E309" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F309" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G309" s="2" t="inlineStr">
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>[Harta Trump Melejit Rp 75 Triliun Sejak Jadi Presiden AS Lagi](https://finance.detik.com/berita-ekonomi-bisnis/d-8555547/harta-trump-melejit-rp-75-triliun-sejak-jadi-presiden-as-lagi)</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F309" t="n">
+        <v>0</v>
+      </c>
+      <c r="G309" t="inlineStr">
         <is>
           <t>detik finance</t>
         </is>
@@ -11400,7 +11400,7 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="D310" s="3" t="inlineStr">
         <is>
-          <t>[Beras IR. III (IR 64)](https://finance.detik.com/info-pangan/jakarta/beras-ir-iii-ir-64)</t>
+          <t>detikFinance - Berita Ekonomi Bisnis, dan Investasi Hari Ini</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="D311" s="3" t="inlineStr">
         <is>
-          <t>[Cabe Merah Keriting](https://finance.detik.com/info-pangan/jakarta/cabe-merah-keriting)</t>
+          <t>[Prabowo: Jadilah Polisi Dekat Rakyat, Gaji Kita dari Rakyat](https://finance.detik.com/berita-ekonomi-bisnis/d-8554838/prabowo-jadilah-polisi-dekat-rakyat-gaji-kita-dari-rakyat)</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
@@ -11463,35 +11463,35 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="inlineStr">
+      <c r="A312" s="4" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="B312" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="C312" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D312" s="3" t="inlineStr">
-        <is>
-          <t>[Daging Sapi Murni (Semur)](https://finance.detik.com/info-pangan/jakarta/daging-sapi-murni-semur)</t>
-        </is>
-      </c>
-      <c r="E312" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F312" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G312" s="2" t="inlineStr">
+      <c r="B312" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C312" s="4" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D312" s="5" t="inlineStr">
+        <is>
+          <t>[Prabowo: Tak Ada Pertumbuhan Ekonomi Tanpa Kepastian Hukum](https://finance.detik.com/berita-ekonomi-bisnis/d-8554797/prabowo-tak-ada-pertumbuhan-ekonomi-tanpa-kepastian-hukum)</t>
+        </is>
+      </c>
+      <c r="E312" s="4" t="inlineStr">
+        <is>
+          <t>POSITIF</t>
+        </is>
+      </c>
+      <c r="F312" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G312" s="4" t="inlineStr">
         <is>
           <t>detik finance</t>
         </is>
@@ -11505,7 +11505,7 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
@@ -11515,7 +11515,7 @@
       </c>
       <c r="D313" s="3" t="inlineStr">
         <is>
-          <t>[Alasan INA Masih Genggam Saham Bank BUMN Saat Pasar Gonjang-ganjing](https://finance.detik.com/bursa-dan-valas/d-8555623/alasan-ina-masih-genggam-saham-bank-bumn-saat-pasar-gonjang-ganjing)</t>
+          <t>[Bandara Husein Sastranegara Ditargetkan Beroperasi Lagi 17 September](https://finance.detik.com/berita-ekonomi-bisnis/d-8554712/bandara-husein-sastranegara-ditargetkan-beroperasi-lagi-17-september)</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
@@ -11533,35 +11533,35 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="inlineStr">
+      <c r="A314" s="6" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="B314" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="C314" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D314" s="3" t="inlineStr">
-        <is>
-          <t>[Toko Online Pungut Pajak Mulai Agustus, Sistem Sudah Siap?](https://finance.detik.com/berita-ekonomi-bisnis/d-8555604/toko-online-pungut-pajak-mulai-agustus-sistem-sudah-siap)</t>
-        </is>
-      </c>
-      <c r="E314" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F314" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G314" s="2" t="inlineStr">
+      <c r="B314" s="6" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C314" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D314" s="7" t="inlineStr">
+        <is>
+          <t>[Harga BBM Diesel Shell &amp; BP Turun, Ini Daftarnya](https://finance.detik.com/energi/d-8554652/harga-bbm-diesel-shell-bp-turun-ini-daftarnya)</t>
+        </is>
+      </c>
+      <c r="E314" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F314" s="6" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G314" s="6" t="inlineStr">
         <is>
           <t>detik finance</t>
         </is>
@@ -11575,7 +11575,7 @@
       </c>
       <c r="B315" s="6" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C315" s="6" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="D315" s="7" t="inlineStr">
         <is>
-          <t>[IHSG Ditutup Menguat Tipis ke 5.695](https://finance.detik.com/bursa-dan-valas/d-8555582/ihsg-ditutup-menguat-tipis-ke-5-695)</t>
+          <t>[Pertamax Tetap! Ini Daftar BBM Pertamina yang Turun Harga](https://finance.detik.com/energi/d-8554611/pertamax-tetap-ini-daftar-bbm-pertamina-yang-turun-harga)</t>
         </is>
       </c>
       <c r="E315" s="6" t="inlineStr">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="D316" s="3" t="inlineStr">
         <is>
-          <t>[Impor Migas RI Makin Bengkak, Paling Banyak dari Singapura](https://finance.detik.com/energi/d-8555589/impor-migas-ri-makin-bengkak-paling-banyak-dari-singapura)</t>
+          <t>[Drone Buatan Bandung Tembus Pasar Australia dan Korea](https://finance.detik.com/foto-bisnis/d-8555166/drone-buatan-bandung-tembus-pasar-australia-dan-korea)</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="D317" s="3" t="inlineStr">
         <is>
-          <t>[DJP Buka Peluang Tambah Toko Online Pungut Pajak](https://finance.detik.com/berita-ekonomi-bisnis/d-8555569/djp-buka-peluang-tambah-toko-online-pungut-pajak)</t>
+          <t>[Beras IR. III (IR 64)](https://finance.detik.com/info-pangan/jakarta/beras-ir-iii-ir-64)</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
@@ -11690,18 +11690,1383 @@
       </c>
       <c r="D318" s="3" t="inlineStr">
         <is>
+          <t>[Cabe Merah Keriting](https://finance.detik.com/info-pangan/jakarta/cabe-merah-keriting)</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D319" s="3" t="inlineStr">
+        <is>
+          <t>[Daging Sapi Murni (Semur)](https://finance.detik.com/info-pangan/jakarta/daging-sapi-murni-semur)</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D320" s="3" t="inlineStr">
+        <is>
+          <t>[Alasan INA Masih Genggam Saham Bank BUMN Saat Pasar Gonjang-ganjing](https://finance.detik.com/bursa-dan-valas/d-8555623/alasan-ina-masih-genggam-saham-bank-bumn-saat-pasar-gonjang-ganjing)</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G320" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D321" s="3" t="inlineStr">
+        <is>
+          <t>[Toko Online Pungut Pajak Mulai Agustus, Sistem Sudah Siap?](https://finance.detik.com/berita-ekonomi-bisnis/d-8555604/toko-online-pungut-pajak-mulai-agustus-sistem-sudah-siap)</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B322" s="6" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C322" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D322" s="7" t="inlineStr">
+        <is>
+          <t>[IHSG Ditutup Menguat Tipis ke 5.695](https://finance.detik.com/bursa-dan-valas/d-8555582/ihsg-ditutup-menguat-tipis-ke-5-695)</t>
+        </is>
+      </c>
+      <c r="E322" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F322" s="6" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G322" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D323" s="3" t="inlineStr">
+        <is>
+          <t>[Impor Migas RI Makin Bengkak, Paling Banyak dari Singapura](https://finance.detik.com/energi/d-8555589/impor-migas-ri-makin-bengkak-paling-banyak-dari-singapura)</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D324" s="3" t="inlineStr">
+        <is>
+          <t>[DJP Buka Peluang Tambah Toko Online Pungut Pajak](https://finance.detik.com/berita-ekonomi-bisnis/d-8555569/djp-buka-peluang-tambah-toko-online-pungut-pajak)</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D325" s="3" t="inlineStr">
+        <is>
           <t>[Harta Trump Melejit Rp 75 Triliun Sejak Jadi Presiden AS Lagi](https://finance.detik.com/berita-ekonomi-bisnis/d-8555547/harta-trump-melejit-rp-75-triliun-sejak-jadi-presiden-as-lagi)</t>
         </is>
       </c>
-      <c r="E318" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F318" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G318" s="2" t="inlineStr">
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G325" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D326" s="3" t="inlineStr">
+        <is>
+          <t>detikFinance - Berita Ekonomi Bisnis, dan Investasi Hari Ini</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D327" s="3" t="inlineStr">
+        <is>
+          <t>[Prabowo: Jadilah Polisi Dekat Rakyat, Gaji Kita dari Rakyat](https://finance.detik.com/berita-ekonomi-bisnis/d-8554838/prabowo-jadilah-polisi-dekat-rakyat-gaji-kita-dari-rakyat)</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B328" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C328" s="4" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D328" s="5" t="inlineStr">
+        <is>
+          <t>[Prabowo: Tak Ada Pertumbuhan Ekonomi Tanpa Kepastian Hukum](https://finance.detik.com/berita-ekonomi-bisnis/d-8554797/prabowo-tak-ada-pertumbuhan-ekonomi-tanpa-kepastian-hukum)</t>
+        </is>
+      </c>
+      <c r="E328" s="4" t="inlineStr">
+        <is>
+          <t>POSITIF</t>
+        </is>
+      </c>
+      <c r="F328" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G328" s="4" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D329" s="3" t="inlineStr">
+        <is>
+          <t>[Bandara Husein Sastranegara Ditargetkan Beroperasi Lagi 17 September](https://finance.detik.com/berita-ekonomi-bisnis/d-8554712/bandara-husein-sastranegara-ditargetkan-beroperasi-lagi-17-september)</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G329" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B330" s="6" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C330" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D330" s="7" t="inlineStr">
+        <is>
+          <t>[Harga BBM Diesel Shell &amp; BP Turun, Ini Daftarnya](https://finance.detik.com/energi/d-8554652/harga-bbm-diesel-shell-bp-turun-ini-daftarnya)</t>
+        </is>
+      </c>
+      <c r="E330" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F330" s="6" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G330" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B331" s="6" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C331" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D331" s="7" t="inlineStr">
+        <is>
+          <t>[Pertamax Tetap! Ini Daftar BBM Pertamina yang Turun Harga](https://finance.detik.com/energi/d-8554611/pertamax-tetap-ini-daftar-bbm-pertamina-yang-turun-harga)</t>
+        </is>
+      </c>
+      <c r="E331" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F331" s="6" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G331" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D332" s="3" t="inlineStr">
+        <is>
+          <t>[Drone Buatan Bandung Tembus Pasar Australia dan Korea](https://finance.detik.com/foto-bisnis/d-8555166/drone-buatan-bandung-tembus-pasar-australia-dan-korea)</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D333" s="3" t="inlineStr">
+        <is>
+          <t>[Beras IR. III (IR 64)](https://finance.detik.com/info-pangan/jakarta/beras-ir-iii-ir-64)</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D334" s="3" t="inlineStr">
+        <is>
+          <t>[Cabe Merah Keriting](https://finance.detik.com/info-pangan/jakarta/cabe-merah-keriting)</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D335" s="3" t="inlineStr">
+        <is>
+          <t>[Daging Sapi Murni (Semur)](https://finance.detik.com/info-pangan/jakarta/daging-sapi-murni-semur)</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D336" s="3" t="inlineStr">
+        <is>
+          <t>[Alasan INA Masih Genggam Saham Bank BUMN Saat Pasar Gonjang-ganjing](https://finance.detik.com/bursa-dan-valas/d-8555623/alasan-ina-masih-genggam-saham-bank-bumn-saat-pasar-gonjang-ganjing)</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D337" s="3" t="inlineStr">
+        <is>
+          <t>[Toko Online Pungut Pajak Mulai Agustus, Sistem Sudah Siap?](https://finance.detik.com/berita-ekonomi-bisnis/d-8555604/toko-online-pungut-pajak-mulai-agustus-sistem-sudah-siap)</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B338" s="6" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C338" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D338" s="7" t="inlineStr">
+        <is>
+          <t>[IHSG Ditutup Menguat Tipis ke 5.695](https://finance.detik.com/bursa-dan-valas/d-8555582/ihsg-ditutup-menguat-tipis-ke-5-695)</t>
+        </is>
+      </c>
+      <c r="E338" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F338" s="6" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G338" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D339" s="3" t="inlineStr">
+        <is>
+          <t>[Impor Migas RI Makin Bengkak, Paling Banyak dari Singapura](https://finance.detik.com/energi/d-8555589/impor-migas-ri-makin-bengkak-paling-banyak-dari-singapura)</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D340" s="3" t="inlineStr">
+        <is>
+          <t>[DJP Buka Peluang Tambah Toko Online Pungut Pajak](https://finance.detik.com/berita-ekonomi-bisnis/d-8555569/djp-buka-peluang-tambah-toko-online-pungut-pajak)</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D341" s="3" t="inlineStr">
+        <is>
+          <t>[Harta Trump Melejit Rp 75 Triliun Sejak Jadi Presiden AS Lagi](https://finance.detik.com/berita-ekonomi-bisnis/d-8555547/harta-trump-melejit-rp-75-triliun-sejak-jadi-presiden-as-lagi)</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D342" s="3" t="inlineStr">
+        <is>
+          <t>detikFinance - Berita Ekonomi Bisnis, dan Investasi Hari Ini</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D343" s="3" t="inlineStr">
+        <is>
+          <t>[Prabowo: Jadilah Polisi Dekat Rakyat, Gaji Kita dari Rakyat](https://finance.detik.com/berita-ekonomi-bisnis/d-8554838/prabowo-jadilah-polisi-dekat-rakyat-gaji-kita-dari-rakyat)</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B344" s="4" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C344" s="4" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D344" s="5" t="inlineStr">
+        <is>
+          <t>[Prabowo: Tak Ada Pertumbuhan Ekonomi Tanpa Kepastian Hukum](https://finance.detik.com/berita-ekonomi-bisnis/d-8554797/prabowo-tak-ada-pertumbuhan-ekonomi-tanpa-kepastian-hukum)</t>
+        </is>
+      </c>
+      <c r="E344" s="4" t="inlineStr">
+        <is>
+          <t>POSITIF</t>
+        </is>
+      </c>
+      <c r="F344" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G344" s="4" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D345" s="3" t="inlineStr">
+        <is>
+          <t>[Bandara Husein Sastranegara Ditargetkan Beroperasi Lagi 17 September](https://finance.detik.com/berita-ekonomi-bisnis/d-8554712/bandara-husein-sastranegara-ditargetkan-beroperasi-lagi-17-september)</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B346" s="6" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C346" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D346" s="7" t="inlineStr">
+        <is>
+          <t>[Harga BBM Diesel Shell &amp; BP Turun, Ini Daftarnya](https://finance.detik.com/energi/d-8554652/harga-bbm-diesel-shell-bp-turun-ini-daftarnya)</t>
+        </is>
+      </c>
+      <c r="E346" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F346" s="6" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G346" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B347" s="6" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C347" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D347" s="7" t="inlineStr">
+        <is>
+          <t>[Pertamax Tetap! Ini Daftar BBM Pertamina yang Turun Harga](https://finance.detik.com/energi/d-8554611/pertamax-tetap-ini-daftar-bbm-pertamina-yang-turun-harga)</t>
+        </is>
+      </c>
+      <c r="E347" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F347" s="6" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G347" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D348" s="3" t="inlineStr">
+        <is>
+          <t>[Drone Buatan Bandung Tembus Pasar Australia dan Korea](https://finance.detik.com/foto-bisnis/d-8555166/drone-buatan-bandung-tembus-pasar-australia-dan-korea)</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G348" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D349" s="3" t="inlineStr">
+        <is>
+          <t>[Beras IR. III (IR 64)](https://finance.detik.com/info-pangan/jakarta/beras-ir-iii-ir-64)</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G349" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D350" s="3" t="inlineStr">
+        <is>
+          <t>[Cabe Merah Keriting](https://finance.detik.com/info-pangan/jakarta/cabe-merah-keriting)</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G350" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D351" s="3" t="inlineStr">
+        <is>
+          <t>[Daging Sapi Murni (Semur)](https://finance.detik.com/info-pangan/jakarta/daging-sapi-murni-semur)</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G351" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D352" s="3" t="inlineStr">
+        <is>
+          <t>[Alasan INA Masih Genggam Saham Bank BUMN Saat Pasar Gonjang-ganjing](https://finance.detik.com/bursa-dan-valas/d-8555623/alasan-ina-masih-genggam-saham-bank-bumn-saat-pasar-gonjang-ganjing)</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G352" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D353" s="3" t="inlineStr">
+        <is>
+          <t>[Toko Online Pungut Pajak Mulai Agustus, Sistem Sudah Siap?](https://finance.detik.com/berita-ekonomi-bisnis/d-8555604/toko-online-pungut-pajak-mulai-agustus-sistem-sudah-siap)</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F353" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G353" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B354" s="6" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C354" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D354" s="7" t="inlineStr">
+        <is>
+          <t>[IHSG Ditutup Menguat Tipis ke 5.695](https://finance.detik.com/bursa-dan-valas/d-8555582/ihsg-ditutup-menguat-tipis-ke-5-695)</t>
+        </is>
+      </c>
+      <c r="E354" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F354" s="6" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G354" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D355" s="3" t="inlineStr">
+        <is>
+          <t>[Impor Migas RI Makin Bengkak, Paling Banyak dari Singapura](https://finance.detik.com/energi/d-8555589/impor-migas-ri-makin-bengkak-paling-banyak-dari-singapura)</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D356" s="3" t="inlineStr">
+        <is>
+          <t>[DJP Buka Peluang Tambah Toko Online Pungut Pajak](https://finance.detik.com/berita-ekonomi-bisnis/d-8555569/djp-buka-peluang-tambah-toko-online-pungut-pajak)</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D357" s="3" t="inlineStr">
+        <is>
+          <t>[Harta Trump Melejit Rp 75 Triliun Sejak Jadi Presiden AS Lagi](https://finance.detik.com/berita-ekonomi-bisnis/d-8555547/harta-trump-melejit-rp-75-triliun-sejak-jadi-presiden-as-lagi)</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G357" s="2" t="inlineStr">
         <is>
           <t>detik finance</t>
         </is>
@@ -11750,7 +13115,7 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>317</v>
+        <v>356</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
@@ -11765,11 +13130,11 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.6%</t>
         </is>
       </c>
     </row>
@@ -11780,11 +13145,11 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>19.4%</t>
         </is>
       </c>
     </row>
@@ -11795,11 +13160,11 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>71.1%</t>
         </is>
       </c>
     </row>
@@ -11810,7 +13175,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="C6" s="8" t="inlineStr"/>
     </row>

--- a/data/sentimen_berita.xlsx
+++ b/data/sentimen_berita.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G357"/>
+  <dimension ref="A1:G373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13067,6 +13067,566 @@
         <v>0</v>
       </c>
       <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D358" s="3" t="inlineStr">
+        <is>
+          <t>detikFinance - Berita Ekonomi Bisnis, dan Investasi Hari Ini</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D359" s="3" t="inlineStr">
+        <is>
+          <t>[Prabowo: Jadilah Polisi Dekat Rakyat, Gaji Kita dari Rakyat](https://finance.detik.com/berita-ekonomi-bisnis/d-8554838/prabowo-jadilah-polisi-dekat-rakyat-gaji-kita-dari-rakyat)</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B360" s="4" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="C360" s="4" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D360" s="5" t="inlineStr">
+        <is>
+          <t>[Prabowo: Tak Ada Pertumbuhan Ekonomi Tanpa Kepastian Hukum](https://finance.detik.com/berita-ekonomi-bisnis/d-8554797/prabowo-tak-ada-pertumbuhan-ekonomi-tanpa-kepastian-hukum)</t>
+        </is>
+      </c>
+      <c r="E360" s="4" t="inlineStr">
+        <is>
+          <t>POSITIF</t>
+        </is>
+      </c>
+      <c r="F360" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G360" s="4" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D361" s="3" t="inlineStr">
+        <is>
+          <t>[Bandara Husein Sastranegara Ditargetkan Beroperasi Lagi 17 September](https://finance.detik.com/berita-ekonomi-bisnis/d-8554712/bandara-husein-sastranegara-ditargetkan-beroperasi-lagi-17-september)</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F361" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B362" s="6" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="C362" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D362" s="7" t="inlineStr">
+        <is>
+          <t>[Harga BBM Diesel Shell &amp; BP Turun, Ini Daftarnya](https://finance.detik.com/energi/d-8554652/harga-bbm-diesel-shell-bp-turun-ini-daftarnya)</t>
+        </is>
+      </c>
+      <c r="E362" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F362" s="6" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G362" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B363" s="6" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="C363" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D363" s="7" t="inlineStr">
+        <is>
+          <t>[Pertamax Tetap! Ini Daftar BBM Pertamina yang Turun Harga](https://finance.detik.com/energi/d-8554611/pertamax-tetap-ini-daftar-bbm-pertamina-yang-turun-harga)</t>
+        </is>
+      </c>
+      <c r="E363" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F363" s="6" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G363" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D364" s="3" t="inlineStr">
+        <is>
+          <t>[Purbaya Lantik Dirjen Anggaran &amp; Dirjen Kekayaan Baru, Ini Sosoknya](https://finance.detik.com/berita-ekonomi-bisnis/d-8555797/purbaya-lantik-dirjen-anggaran-dirjen-kekayaan-baru-ini-sosoknya)</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D365" s="3" t="inlineStr">
+        <is>
+          <t>[Purbaya Ancam Potong Anggaran Daerah yang Hambat Investasi](https://finance.detik.com/berita-ekonomi-bisnis/d-8550652/purbaya-ancam-potong-anggaran-daerah-yang-hambat-investasi)</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D366" s="3" t="inlineStr">
+        <is>
+          <t>[Purbaya Mulai Tarik Dana Rp 300 T dari Bank BUMN](https://finance.detik.com/berita-ekonomi-bisnis/d-8546379/purbaya-mulai-tarik-dana-rp-300-t-dari-bank-bumn)</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D367" s="3" t="inlineStr">
+        <is>
+          <t>[Beras IR. III (IR 64)](https://finance.detik.com/info-pangan/jakarta/beras-ir-iii-ir-64)</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F367" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D368" s="3" t="inlineStr">
+        <is>
+          <t>[Cabe Merah Keriting](https://finance.detik.com/info-pangan/jakarta/cabe-merah-keriting)</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D369" s="3" t="inlineStr">
+        <is>
+          <t>[Daging Sapi Murni (Semur)](https://finance.detik.com/info-pangan/jakarta/daging-sapi-murni-semur)</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D370" s="3" t="inlineStr">
+        <is>
+          <t>[Pertamina Kerja Sama dengan Pupuk Indonesia untuk Dukung Ketahanan Pangan](https://finance.detik.com/berita-ekonomi-bisnis/d-8555820/pertamina-kerja-sama-dengan-pupuk-indonesia-untuk-dukung-ketahanan-pangan)</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D371" s="3" t="inlineStr">
+        <is>
+          <t>[Drone Buatan Bandung Tembus Pasar Australia dan Korea](https://finance.detik.com/foto-bisnis/d-8555166/drone-buatan-bandung-tembus-pasar-australia-dan-korea)</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F371" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G371" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D372" s="3" t="inlineStr">
+        <is>
+          <t>[Alasan INA Masih Genggam Saham Bank BUMN Saat Pasar Gonjang-ganjing](https://finance.detik.com/bursa-dan-valas/d-8555623/alasan-ina-masih-genggam-saham-bank-bumn-saat-pasar-gonjang-ganjing)</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D373" s="3" t="inlineStr">
+        <is>
+          <t>[Toko Online Pungut Pajak Mulai Agustus, Sistem Sudah Siap?](https://finance.detik.com/berita-ekonomi-bisnis/d-8555604/toko-online-pungut-pajak-mulai-agustus-sistem-sudah-siap)</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G373" s="2" t="inlineStr">
         <is>
           <t>detik finance</t>
         </is>
@@ -13115,7 +13675,7 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
@@ -13130,11 +13690,11 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.4%</t>
         </is>
       </c>
     </row>
@@ -13145,11 +13705,11 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>19.1%</t>
         </is>
       </c>
     </row>
@@ -13160,11 +13720,11 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>71.5%</t>
         </is>
       </c>
     </row>
@@ -13175,7 +13735,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="C6" s="8" t="inlineStr"/>
     </row>

--- a/data/sentimen_berita.xlsx
+++ b/data/sentimen_berita.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G373"/>
+  <dimension ref="A1:G389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13627,6 +13627,566 @@
         <v>0</v>
       </c>
       <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D374" s="3" t="inlineStr">
+        <is>
+          <t>detikFinance - Berita Ekonomi Bisnis, dan Investasi Hari Ini</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D375" s="3" t="inlineStr">
+        <is>
+          <t>[Prabowo: Jadilah Polisi Dekat Rakyat, Gaji Kita dari Rakyat](https://finance.detik.com/berita-ekonomi-bisnis/d-8554838/prabowo-jadilah-polisi-dekat-rakyat-gaji-kita-dari-rakyat)</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B376" s="4" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C376" s="4" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D376" s="5" t="inlineStr">
+        <is>
+          <t>[Prabowo: Tak Ada Pertumbuhan Ekonomi Tanpa Kepastian Hukum](https://finance.detik.com/berita-ekonomi-bisnis/d-8554797/prabowo-tak-ada-pertumbuhan-ekonomi-tanpa-kepastian-hukum)</t>
+        </is>
+      </c>
+      <c r="E376" s="4" t="inlineStr">
+        <is>
+          <t>POSITIF</t>
+        </is>
+      </c>
+      <c r="F376" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G376" s="4" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D377" s="3" t="inlineStr">
+        <is>
+          <t>[Bandara Husein Sastranegara Ditargetkan Beroperasi Lagi 17 September](https://finance.detik.com/berita-ekonomi-bisnis/d-8554712/bandara-husein-sastranegara-ditargetkan-beroperasi-lagi-17-september)</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B378" s="6" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C378" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D378" s="7" t="inlineStr">
+        <is>
+          <t>[Harga BBM Diesel Shell &amp; BP Turun, Ini Daftarnya](https://finance.detik.com/energi/d-8554652/harga-bbm-diesel-shell-bp-turun-ini-daftarnya)</t>
+        </is>
+      </c>
+      <c r="E378" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F378" s="6" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G378" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B379" s="6" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C379" s="6" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D379" s="7" t="inlineStr">
+        <is>
+          <t>[Pertamax Tetap! Ini Daftar BBM Pertamina yang Turun Harga](https://finance.detik.com/energi/d-8554611/pertamax-tetap-ini-daftar-bbm-pertamina-yang-turun-harga)</t>
+        </is>
+      </c>
+      <c r="E379" s="6" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F379" s="6" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G379" s="6" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D380" s="3" t="inlineStr">
+        <is>
+          <t>[Purbaya Lantik Dirjen Anggaran &amp; Dirjen Kekayaan Baru, Ini Sosoknya](https://finance.detik.com/berita-ekonomi-bisnis/d-8555797/purbaya-lantik-dirjen-anggaran-dirjen-kekayaan-baru-ini-sosoknya)</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D381" s="3" t="inlineStr">
+        <is>
+          <t>[Purbaya Ancam Potong Anggaran Daerah yang Hambat Investasi](https://finance.detik.com/berita-ekonomi-bisnis/d-8550652/purbaya-ancam-potong-anggaran-daerah-yang-hambat-investasi)</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D382" s="3" t="inlineStr">
+        <is>
+          <t>[Purbaya Mulai Tarik Dana Rp 300 T dari Bank BUMN](https://finance.detik.com/berita-ekonomi-bisnis/d-8546379/purbaya-mulai-tarik-dana-rp-300-t-dari-bank-bumn)</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D383" s="3" t="inlineStr">
+        <is>
+          <t>[Beras IR. III (IR 64)](https://finance.detik.com/info-pangan/jakarta/beras-ir-iii-ir-64)</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D384" s="3" t="inlineStr">
+        <is>
+          <t>[Cabe Merah Keriting](https://finance.detik.com/info-pangan/jakarta/cabe-merah-keriting)</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D385" s="3" t="inlineStr">
+        <is>
+          <t>[Daging Sapi Murni (Semur)](https://finance.detik.com/info-pangan/jakarta/daging-sapi-murni-semur)</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D386" s="3" t="inlineStr">
+        <is>
+          <t>[Pertamina Kerja Sama dengan Pupuk Indonesia untuk Dukung Ketahanan Pangan](https://finance.detik.com/berita-ekonomi-bisnis/d-8555820/pertamina-kerja-sama-dengan-pupuk-indonesia-untuk-dukung-ketahanan-pangan)</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D387" s="3" t="inlineStr">
+        <is>
+          <t>[Drone Buatan Bandung Tembus Pasar Australia dan Korea](https://finance.detik.com/foto-bisnis/d-8555166/drone-buatan-bandung-tembus-pasar-australia-dan-korea)</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D388" s="3" t="inlineStr">
+        <is>
+          <t>[Alasan INA Masih Genggam Saham Bank BUMN Saat Pasar Gonjang-ganjing](https://finance.detik.com/bursa-dan-valas/d-8555623/alasan-ina-masih-genggam-saham-bank-bumn-saat-pasar-gonjang-ganjing)</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D389" s="3" t="inlineStr">
+        <is>
+          <t>[Toko Online Pungut Pajak Mulai Agustus, Sistem Sudah Siap?](https://finance.detik.com/berita-ekonomi-bisnis/d-8555604/toko-online-pungut-pajak-mulai-agustus-sistem-sudah-siap)</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G389" s="2" t="inlineStr">
         <is>
           <t>detik finance</t>
         </is>
@@ -13675,7 +14235,7 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
@@ -13690,11 +14250,11 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
     </row>
@@ -13705,11 +14265,11 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
     </row>
@@ -13720,11 +14280,11 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>71.9%</t>
         </is>
       </c>
     </row>
@@ -13735,7 +14295,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="C6" s="8" t="inlineStr"/>
     </row>

--- a/data/sentimen_berita.xlsx
+++ b/data/sentimen_berita.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Detail" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Ringkasan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -190,14 +190,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -220,7 +219,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -248,7 +247,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -263,9 +262,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -563,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G389"/>
+  <dimension ref="A1:G317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9650,7 +9649,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9685,7 +9684,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9720,7 +9719,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9755,7 +9754,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9790,7 +9789,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9930,7 +9929,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9965,7 +9964,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -10000,7 +9999,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -10210,7 +10209,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -10665,7 +10664,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -11155,7 +11154,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -11190,7 +11189,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -11225,7 +11224,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -11260,7 +11259,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -11295,7 +11294,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -11330,7 +11329,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -11365,7 +11364,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -11393,2800 +11392,280 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="inlineStr">
+      <c r="A310" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="B310" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C310" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D310" s="3" t="inlineStr">
-        <is>
-          <t>detikFinance - Berita Ekonomi Bisnis, dan Investasi Hari Ini</t>
-        </is>
-      </c>
-      <c r="E310" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F310" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G310" s="2" t="inlineStr">
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>[Purbaya Lantik Dirjen Anggaran &amp; Dirjen Kekayaan Baru, Ini Sosoknya](https://finance.detik.com/berita-ekonomi-bisnis/d-8555797/purbaya-lantik-dirjen-anggaran-dirjen-kekayaan-baru-ini-sosoknya)</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F310" t="n">
+        <v>0</v>
+      </c>
+      <c r="G310" t="inlineStr">
         <is>
           <t>detik finance</t>
         </is>
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="inlineStr">
+      <c r="A311" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="B311" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C311" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D311" s="3" t="inlineStr">
-        <is>
-          <t>[Prabowo: Jadilah Polisi Dekat Rakyat, Gaji Kita dari Rakyat](https://finance.detik.com/berita-ekonomi-bisnis/d-8554838/prabowo-jadilah-polisi-dekat-rakyat-gaji-kita-dari-rakyat)</t>
-        </is>
-      </c>
-      <c r="E311" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F311" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G311" s="2" t="inlineStr">
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>[Purbaya Ancam Potong Anggaran Daerah yang Hambat Investasi](https://finance.detik.com/berita-ekonomi-bisnis/d-8550652/purbaya-ancam-potong-anggaran-daerah-yang-hambat-investasi)</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F311" t="n">
+        <v>0</v>
+      </c>
+      <c r="G311" t="inlineStr">
         <is>
           <t>detik finance</t>
         </is>
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="4" t="inlineStr">
+      <c r="A312" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="B312" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C312" s="4" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D312" s="5" t="inlineStr">
-        <is>
-          <t>[Prabowo: Tak Ada Pertumbuhan Ekonomi Tanpa Kepastian Hukum](https://finance.detik.com/berita-ekonomi-bisnis/d-8554797/prabowo-tak-ada-pertumbuhan-ekonomi-tanpa-kepastian-hukum)</t>
-        </is>
-      </c>
-      <c r="E312" s="4" t="inlineStr">
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>[Purbaya Mulai Tarik Dana Rp 300 T dari Bank BUMN](https://finance.detik.com/berita-ekonomi-bisnis/d-8546379/purbaya-mulai-tarik-dana-rp-300-t-dari-bank-bumn)</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F312" t="n">
+        <v>0</v>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>[Pertamina Kerja Sama dengan Pupuk Indonesia untuk Dukung Ketahanan Pangan](https://finance.detik.com/berita-ekonomi-bisnis/d-8555820/pertamina-kerja-sama-dengan-pupuk-indonesia-untuk-dukung-ketahanan-pangan)</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F313" t="n">
+        <v>0</v>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>[Penasihat Khusus Presiden Bicara Nasib PT Granito, Singgung Danantara](https://finance.detik.com/berita-ekonomi-bisnis/d-8555948/penasihat-khusus-presiden-bicara-nasib-pt-granito-singgung-danantara)</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F314" t="n">
+        <v>0</v>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>[Sengketa Pekerja Newcrest, Jadi Preseden Buruk Tata Kelola Divestasi Asing](https://finance.detik.com/berita-ekonomi-bisnis/d-8554362/sengketa-pekerja-newcrest-jadi-preseden-buruk-tata-kelola-divestasi-asing)</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>NEGATIF</t>
+        </is>
+      </c>
+      <c r="F315" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>[Purbaya ke Dirjen Baru: Tidak Semua Permintaan Anggaran Harus Dipenuhi!](https://finance.detik.com/berita-ekonomi-bisnis/d-8555924/purbaya-ke-dirjen-baru-tidak-semua-permintaan-anggaran-harus-dipenuhi)</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F316" t="n">
+        <v>0</v>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>detik finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>[Surplus Neraca Dagang Terhenti, Purbaya Duga karena Impor Migas Naik](https://finance.detik.com/berita-ekonomi-bisnis/d-8555912/surplus-neraca-dagang-terhenti-purbaya-duga-karena-impor-migas-naik)</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
         <is>
           <t>POSITIF</t>
         </is>
       </c>
-      <c r="F312" s="4" t="n">
+      <c r="F317" t="n">
         <v>0.65</v>
       </c>
-      <c r="G312" s="4" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B313" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C313" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D313" s="3" t="inlineStr">
-        <is>
-          <t>[Bandara Husein Sastranegara Ditargetkan Beroperasi Lagi 17 September](https://finance.detik.com/berita-ekonomi-bisnis/d-8554712/bandara-husein-sastranegara-ditargetkan-beroperasi-lagi-17-september)</t>
-        </is>
-      </c>
-      <c r="E313" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F313" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G313" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B314" s="6" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C314" s="6" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D314" s="7" t="inlineStr">
-        <is>
-          <t>[Harga BBM Diesel Shell &amp; BP Turun, Ini Daftarnya](https://finance.detik.com/energi/d-8554652/harga-bbm-diesel-shell-bp-turun-ini-daftarnya)</t>
-        </is>
-      </c>
-      <c r="E314" s="6" t="inlineStr">
-        <is>
-          <t>NEGATIF</t>
-        </is>
-      </c>
-      <c r="F314" s="6" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="G314" s="6" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B315" s="6" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C315" s="6" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D315" s="7" t="inlineStr">
-        <is>
-          <t>[Pertamax Tetap! Ini Daftar BBM Pertamina yang Turun Harga](https://finance.detik.com/energi/d-8554611/pertamax-tetap-ini-daftar-bbm-pertamina-yang-turun-harga)</t>
-        </is>
-      </c>
-      <c r="E315" s="6" t="inlineStr">
-        <is>
-          <t>NEGATIF</t>
-        </is>
-      </c>
-      <c r="F315" s="6" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="G315" s="6" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B316" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C316" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D316" s="3" t="inlineStr">
-        <is>
-          <t>[Drone Buatan Bandung Tembus Pasar Australia dan Korea](https://finance.detik.com/foto-bisnis/d-8555166/drone-buatan-bandung-tembus-pasar-australia-dan-korea)</t>
-        </is>
-      </c>
-      <c r="E316" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F316" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G316" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B317" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C317" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D317" s="3" t="inlineStr">
-        <is>
-          <t>[Beras IR. III (IR 64)](https://finance.detik.com/info-pangan/jakarta/beras-ir-iii-ir-64)</t>
-        </is>
-      </c>
-      <c r="E317" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F317" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G317" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B318" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C318" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D318" s="3" t="inlineStr">
-        <is>
-          <t>[Cabe Merah Keriting](https://finance.detik.com/info-pangan/jakarta/cabe-merah-keriting)</t>
-        </is>
-      </c>
-      <c r="E318" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F318" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G318" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B319" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C319" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D319" s="3" t="inlineStr">
-        <is>
-          <t>[Daging Sapi Murni (Semur)](https://finance.detik.com/info-pangan/jakarta/daging-sapi-murni-semur)</t>
-        </is>
-      </c>
-      <c r="E319" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F319" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G319" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B320" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C320" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D320" s="3" t="inlineStr">
-        <is>
-          <t>[Alasan INA Masih Genggam Saham Bank BUMN Saat Pasar Gonjang-ganjing](https://finance.detik.com/bursa-dan-valas/d-8555623/alasan-ina-masih-genggam-saham-bank-bumn-saat-pasar-gonjang-ganjing)</t>
-        </is>
-      </c>
-      <c r="E320" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F320" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G320" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B321" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C321" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D321" s="3" t="inlineStr">
-        <is>
-          <t>[Toko Online Pungut Pajak Mulai Agustus, Sistem Sudah Siap?](https://finance.detik.com/berita-ekonomi-bisnis/d-8555604/toko-online-pungut-pajak-mulai-agustus-sistem-sudah-siap)</t>
-        </is>
-      </c>
-      <c r="E321" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F321" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G321" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B322" s="6" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C322" s="6" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D322" s="7" t="inlineStr">
-        <is>
-          <t>[IHSG Ditutup Menguat Tipis ke 5.695](https://finance.detik.com/bursa-dan-valas/d-8555582/ihsg-ditutup-menguat-tipis-ke-5-695)</t>
-        </is>
-      </c>
-      <c r="E322" s="6" t="inlineStr">
-        <is>
-          <t>NEGATIF</t>
-        </is>
-      </c>
-      <c r="F322" s="6" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="G322" s="6" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B323" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C323" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D323" s="3" t="inlineStr">
-        <is>
-          <t>[Impor Migas RI Makin Bengkak, Paling Banyak dari Singapura](https://finance.detik.com/energi/d-8555589/impor-migas-ri-makin-bengkak-paling-banyak-dari-singapura)</t>
-        </is>
-      </c>
-      <c r="E323" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F323" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G323" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B324" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C324" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D324" s="3" t="inlineStr">
-        <is>
-          <t>[DJP Buka Peluang Tambah Toko Online Pungut Pajak](https://finance.detik.com/berita-ekonomi-bisnis/d-8555569/djp-buka-peluang-tambah-toko-online-pungut-pajak)</t>
-        </is>
-      </c>
-      <c r="E324" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F324" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G324" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B325" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C325" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D325" s="3" t="inlineStr">
-        <is>
-          <t>[Harta Trump Melejit Rp 75 Triliun Sejak Jadi Presiden AS Lagi](https://finance.detik.com/berita-ekonomi-bisnis/d-8555547/harta-trump-melejit-rp-75-triliun-sejak-jadi-presiden-as-lagi)</t>
-        </is>
-      </c>
-      <c r="E325" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F325" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G325" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B326" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C326" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D326" s="3" t="inlineStr">
-        <is>
-          <t>detikFinance - Berita Ekonomi Bisnis, dan Investasi Hari Ini</t>
-        </is>
-      </c>
-      <c r="E326" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F326" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G326" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B327" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C327" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D327" s="3" t="inlineStr">
-        <is>
-          <t>[Prabowo: Jadilah Polisi Dekat Rakyat, Gaji Kita dari Rakyat](https://finance.detik.com/berita-ekonomi-bisnis/d-8554838/prabowo-jadilah-polisi-dekat-rakyat-gaji-kita-dari-rakyat)</t>
-        </is>
-      </c>
-      <c r="E327" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F327" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G327" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B328" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C328" s="4" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D328" s="5" t="inlineStr">
-        <is>
-          <t>[Prabowo: Tak Ada Pertumbuhan Ekonomi Tanpa Kepastian Hukum](https://finance.detik.com/berita-ekonomi-bisnis/d-8554797/prabowo-tak-ada-pertumbuhan-ekonomi-tanpa-kepastian-hukum)</t>
-        </is>
-      </c>
-      <c r="E328" s="4" t="inlineStr">
-        <is>
-          <t>POSITIF</t>
-        </is>
-      </c>
-      <c r="F328" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G328" s="4" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B329" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C329" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D329" s="3" t="inlineStr">
-        <is>
-          <t>[Bandara Husein Sastranegara Ditargetkan Beroperasi Lagi 17 September](https://finance.detik.com/berita-ekonomi-bisnis/d-8554712/bandara-husein-sastranegara-ditargetkan-beroperasi-lagi-17-september)</t>
-        </is>
-      </c>
-      <c r="E329" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F329" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G329" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B330" s="6" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C330" s="6" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D330" s="7" t="inlineStr">
-        <is>
-          <t>[Harga BBM Diesel Shell &amp; BP Turun, Ini Daftarnya](https://finance.detik.com/energi/d-8554652/harga-bbm-diesel-shell-bp-turun-ini-daftarnya)</t>
-        </is>
-      </c>
-      <c r="E330" s="6" t="inlineStr">
-        <is>
-          <t>NEGATIF</t>
-        </is>
-      </c>
-      <c r="F330" s="6" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="G330" s="6" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B331" s="6" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C331" s="6" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D331" s="7" t="inlineStr">
-        <is>
-          <t>[Pertamax Tetap! Ini Daftar BBM Pertamina yang Turun Harga](https://finance.detik.com/energi/d-8554611/pertamax-tetap-ini-daftar-bbm-pertamina-yang-turun-harga)</t>
-        </is>
-      </c>
-      <c r="E331" s="6" t="inlineStr">
-        <is>
-          <t>NEGATIF</t>
-        </is>
-      </c>
-      <c r="F331" s="6" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="G331" s="6" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B332" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C332" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D332" s="3" t="inlineStr">
-        <is>
-          <t>[Drone Buatan Bandung Tembus Pasar Australia dan Korea](https://finance.detik.com/foto-bisnis/d-8555166/drone-buatan-bandung-tembus-pasar-australia-dan-korea)</t>
-        </is>
-      </c>
-      <c r="E332" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F332" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G332" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B333" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C333" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D333" s="3" t="inlineStr">
-        <is>
-          <t>[Beras IR. III (IR 64)](https://finance.detik.com/info-pangan/jakarta/beras-ir-iii-ir-64)</t>
-        </is>
-      </c>
-      <c r="E333" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F333" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G333" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B334" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C334" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D334" s="3" t="inlineStr">
-        <is>
-          <t>[Cabe Merah Keriting](https://finance.detik.com/info-pangan/jakarta/cabe-merah-keriting)</t>
-        </is>
-      </c>
-      <c r="E334" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F334" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G334" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B335" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C335" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D335" s="3" t="inlineStr">
-        <is>
-          <t>[Daging Sapi Murni (Semur)](https://finance.detik.com/info-pangan/jakarta/daging-sapi-murni-semur)</t>
-        </is>
-      </c>
-      <c r="E335" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F335" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G335" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B336" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C336" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D336" s="3" t="inlineStr">
-        <is>
-          <t>[Alasan INA Masih Genggam Saham Bank BUMN Saat Pasar Gonjang-ganjing](https://finance.detik.com/bursa-dan-valas/d-8555623/alasan-ina-masih-genggam-saham-bank-bumn-saat-pasar-gonjang-ganjing)</t>
-        </is>
-      </c>
-      <c r="E336" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F336" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G336" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B337" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C337" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D337" s="3" t="inlineStr">
-        <is>
-          <t>[Toko Online Pungut Pajak Mulai Agustus, Sistem Sudah Siap?](https://finance.detik.com/berita-ekonomi-bisnis/d-8555604/toko-online-pungut-pajak-mulai-agustus-sistem-sudah-siap)</t>
-        </is>
-      </c>
-      <c r="E337" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F337" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G337" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B338" s="6" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C338" s="6" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D338" s="7" t="inlineStr">
-        <is>
-          <t>[IHSG Ditutup Menguat Tipis ke 5.695](https://finance.detik.com/bursa-dan-valas/d-8555582/ihsg-ditutup-menguat-tipis-ke-5-695)</t>
-        </is>
-      </c>
-      <c r="E338" s="6" t="inlineStr">
-        <is>
-          <t>NEGATIF</t>
-        </is>
-      </c>
-      <c r="F338" s="6" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="G338" s="6" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B339" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C339" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D339" s="3" t="inlineStr">
-        <is>
-          <t>[Impor Migas RI Makin Bengkak, Paling Banyak dari Singapura](https://finance.detik.com/energi/d-8555589/impor-migas-ri-makin-bengkak-paling-banyak-dari-singapura)</t>
-        </is>
-      </c>
-      <c r="E339" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F339" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G339" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B340" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C340" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D340" s="3" t="inlineStr">
-        <is>
-          <t>[DJP Buka Peluang Tambah Toko Online Pungut Pajak](https://finance.detik.com/berita-ekonomi-bisnis/d-8555569/djp-buka-peluang-tambah-toko-online-pungut-pajak)</t>
-        </is>
-      </c>
-      <c r="E340" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F340" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G340" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B341" s="2" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C341" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D341" s="3" t="inlineStr">
-        <is>
-          <t>[Harta Trump Melejit Rp 75 Triliun Sejak Jadi Presiden AS Lagi](https://finance.detik.com/berita-ekonomi-bisnis/d-8555547/harta-trump-melejit-rp-75-triliun-sejak-jadi-presiden-as-lagi)</t>
-        </is>
-      </c>
-      <c r="E341" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F341" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G341" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B342" s="2" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="C342" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D342" s="3" t="inlineStr">
-        <is>
-          <t>detikFinance - Berita Ekonomi Bisnis, dan Investasi Hari Ini</t>
-        </is>
-      </c>
-      <c r="E342" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F342" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G342" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B343" s="2" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="C343" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D343" s="3" t="inlineStr">
-        <is>
-          <t>[Prabowo: Jadilah Polisi Dekat Rakyat, Gaji Kita dari Rakyat](https://finance.detik.com/berita-ekonomi-bisnis/d-8554838/prabowo-jadilah-polisi-dekat-rakyat-gaji-kita-dari-rakyat)</t>
-        </is>
-      </c>
-      <c r="E343" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F343" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G343" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B344" s="4" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="C344" s="4" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D344" s="5" t="inlineStr">
-        <is>
-          <t>[Prabowo: Tak Ada Pertumbuhan Ekonomi Tanpa Kepastian Hukum](https://finance.detik.com/berita-ekonomi-bisnis/d-8554797/prabowo-tak-ada-pertumbuhan-ekonomi-tanpa-kepastian-hukum)</t>
-        </is>
-      </c>
-      <c r="E344" s="4" t="inlineStr">
-        <is>
-          <t>POSITIF</t>
-        </is>
-      </c>
-      <c r="F344" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G344" s="4" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B345" s="2" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="C345" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D345" s="3" t="inlineStr">
-        <is>
-          <t>[Bandara Husein Sastranegara Ditargetkan Beroperasi Lagi 17 September](https://finance.detik.com/berita-ekonomi-bisnis/d-8554712/bandara-husein-sastranegara-ditargetkan-beroperasi-lagi-17-september)</t>
-        </is>
-      </c>
-      <c r="E345" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F345" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G345" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B346" s="6" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="C346" s="6" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D346" s="7" t="inlineStr">
-        <is>
-          <t>[Harga BBM Diesel Shell &amp; BP Turun, Ini Daftarnya](https://finance.detik.com/energi/d-8554652/harga-bbm-diesel-shell-bp-turun-ini-daftarnya)</t>
-        </is>
-      </c>
-      <c r="E346" s="6" t="inlineStr">
-        <is>
-          <t>NEGATIF</t>
-        </is>
-      </c>
-      <c r="F346" s="6" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="G346" s="6" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B347" s="6" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="C347" s="6" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D347" s="7" t="inlineStr">
-        <is>
-          <t>[Pertamax Tetap! Ini Daftar BBM Pertamina yang Turun Harga](https://finance.detik.com/energi/d-8554611/pertamax-tetap-ini-daftar-bbm-pertamina-yang-turun-harga)</t>
-        </is>
-      </c>
-      <c r="E347" s="6" t="inlineStr">
-        <is>
-          <t>NEGATIF</t>
-        </is>
-      </c>
-      <c r="F347" s="6" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="G347" s="6" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B348" s="2" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="C348" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D348" s="3" t="inlineStr">
-        <is>
-          <t>[Drone Buatan Bandung Tembus Pasar Australia dan Korea](https://finance.detik.com/foto-bisnis/d-8555166/drone-buatan-bandung-tembus-pasar-australia-dan-korea)</t>
-        </is>
-      </c>
-      <c r="E348" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F348" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G348" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B349" s="2" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="C349" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D349" s="3" t="inlineStr">
-        <is>
-          <t>[Beras IR. III (IR 64)](https://finance.detik.com/info-pangan/jakarta/beras-ir-iii-ir-64)</t>
-        </is>
-      </c>
-      <c r="E349" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F349" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G349" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B350" s="2" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="C350" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D350" s="3" t="inlineStr">
-        <is>
-          <t>[Cabe Merah Keriting](https://finance.detik.com/info-pangan/jakarta/cabe-merah-keriting)</t>
-        </is>
-      </c>
-      <c r="E350" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F350" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G350" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B351" s="2" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="C351" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D351" s="3" t="inlineStr">
-        <is>
-          <t>[Daging Sapi Murni (Semur)](https://finance.detik.com/info-pangan/jakarta/daging-sapi-murni-semur)</t>
-        </is>
-      </c>
-      <c r="E351" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F351" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G351" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B352" s="2" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="C352" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D352" s="3" t="inlineStr">
-        <is>
-          <t>[Alasan INA Masih Genggam Saham Bank BUMN Saat Pasar Gonjang-ganjing](https://finance.detik.com/bursa-dan-valas/d-8555623/alasan-ina-masih-genggam-saham-bank-bumn-saat-pasar-gonjang-ganjing)</t>
-        </is>
-      </c>
-      <c r="E352" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F352" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G352" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B353" s="2" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="C353" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D353" s="3" t="inlineStr">
-        <is>
-          <t>[Toko Online Pungut Pajak Mulai Agustus, Sistem Sudah Siap?](https://finance.detik.com/berita-ekonomi-bisnis/d-8555604/toko-online-pungut-pajak-mulai-agustus-sistem-sudah-siap)</t>
-        </is>
-      </c>
-      <c r="E353" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F353" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G353" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B354" s="6" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="C354" s="6" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D354" s="7" t="inlineStr">
-        <is>
-          <t>[IHSG Ditutup Menguat Tipis ke 5.695](https://finance.detik.com/bursa-dan-valas/d-8555582/ihsg-ditutup-menguat-tipis-ke-5-695)</t>
-        </is>
-      </c>
-      <c r="E354" s="6" t="inlineStr">
-        <is>
-          <t>NEGATIF</t>
-        </is>
-      </c>
-      <c r="F354" s="6" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="G354" s="6" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B355" s="2" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="C355" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D355" s="3" t="inlineStr">
-        <is>
-          <t>[Impor Migas RI Makin Bengkak, Paling Banyak dari Singapura](https://finance.detik.com/energi/d-8555589/impor-migas-ri-makin-bengkak-paling-banyak-dari-singapura)</t>
-        </is>
-      </c>
-      <c r="E355" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F355" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G355" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B356" s="2" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="C356" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D356" s="3" t="inlineStr">
-        <is>
-          <t>[DJP Buka Peluang Tambah Toko Online Pungut Pajak](https://finance.detik.com/berita-ekonomi-bisnis/d-8555569/djp-buka-peluang-tambah-toko-online-pungut-pajak)</t>
-        </is>
-      </c>
-      <c r="E356" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F356" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G356" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B357" s="2" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="C357" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D357" s="3" t="inlineStr">
-        <is>
-          <t>[Harta Trump Melejit Rp 75 Triliun Sejak Jadi Presiden AS Lagi](https://finance.detik.com/berita-ekonomi-bisnis/d-8555547/harta-trump-melejit-rp-75-triliun-sejak-jadi-presiden-as-lagi)</t>
-        </is>
-      </c>
-      <c r="E357" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F357" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G357" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B358" s="2" t="inlineStr">
-        <is>
-          <t>20:31</t>
-        </is>
-      </c>
-      <c r="C358" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D358" s="3" t="inlineStr">
-        <is>
-          <t>detikFinance - Berita Ekonomi Bisnis, dan Investasi Hari Ini</t>
-        </is>
-      </c>
-      <c r="E358" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F358" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G358" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B359" s="2" t="inlineStr">
-        <is>
-          <t>20:31</t>
-        </is>
-      </c>
-      <c r="C359" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D359" s="3" t="inlineStr">
-        <is>
-          <t>[Prabowo: Jadilah Polisi Dekat Rakyat, Gaji Kita dari Rakyat](https://finance.detik.com/berita-ekonomi-bisnis/d-8554838/prabowo-jadilah-polisi-dekat-rakyat-gaji-kita-dari-rakyat)</t>
-        </is>
-      </c>
-      <c r="E359" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F359" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G359" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B360" s="4" t="inlineStr">
-        <is>
-          <t>20:31</t>
-        </is>
-      </c>
-      <c r="C360" s="4" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D360" s="5" t="inlineStr">
-        <is>
-          <t>[Prabowo: Tak Ada Pertumbuhan Ekonomi Tanpa Kepastian Hukum](https://finance.detik.com/berita-ekonomi-bisnis/d-8554797/prabowo-tak-ada-pertumbuhan-ekonomi-tanpa-kepastian-hukum)</t>
-        </is>
-      </c>
-      <c r="E360" s="4" t="inlineStr">
-        <is>
-          <t>POSITIF</t>
-        </is>
-      </c>
-      <c r="F360" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G360" s="4" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B361" s="2" t="inlineStr">
-        <is>
-          <t>20:31</t>
-        </is>
-      </c>
-      <c r="C361" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D361" s="3" t="inlineStr">
-        <is>
-          <t>[Bandara Husein Sastranegara Ditargetkan Beroperasi Lagi 17 September](https://finance.detik.com/berita-ekonomi-bisnis/d-8554712/bandara-husein-sastranegara-ditargetkan-beroperasi-lagi-17-september)</t>
-        </is>
-      </c>
-      <c r="E361" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F361" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G361" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B362" s="6" t="inlineStr">
-        <is>
-          <t>20:31</t>
-        </is>
-      </c>
-      <c r="C362" s="6" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D362" s="7" t="inlineStr">
-        <is>
-          <t>[Harga BBM Diesel Shell &amp; BP Turun, Ini Daftarnya](https://finance.detik.com/energi/d-8554652/harga-bbm-diesel-shell-bp-turun-ini-daftarnya)</t>
-        </is>
-      </c>
-      <c r="E362" s="6" t="inlineStr">
-        <is>
-          <t>NEGATIF</t>
-        </is>
-      </c>
-      <c r="F362" s="6" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="G362" s="6" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B363" s="6" t="inlineStr">
-        <is>
-          <t>20:31</t>
-        </is>
-      </c>
-      <c r="C363" s="6" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D363" s="7" t="inlineStr">
-        <is>
-          <t>[Pertamax Tetap! Ini Daftar BBM Pertamina yang Turun Harga](https://finance.detik.com/energi/d-8554611/pertamax-tetap-ini-daftar-bbm-pertamina-yang-turun-harga)</t>
-        </is>
-      </c>
-      <c r="E363" s="6" t="inlineStr">
-        <is>
-          <t>NEGATIF</t>
-        </is>
-      </c>
-      <c r="F363" s="6" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="G363" s="6" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B364" s="2" t="inlineStr">
-        <is>
-          <t>20:31</t>
-        </is>
-      </c>
-      <c r="C364" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D364" s="3" t="inlineStr">
-        <is>
-          <t>[Purbaya Lantik Dirjen Anggaran &amp; Dirjen Kekayaan Baru, Ini Sosoknya](https://finance.detik.com/berita-ekonomi-bisnis/d-8555797/purbaya-lantik-dirjen-anggaran-dirjen-kekayaan-baru-ini-sosoknya)</t>
-        </is>
-      </c>
-      <c r="E364" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F364" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G364" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B365" s="2" t="inlineStr">
-        <is>
-          <t>20:31</t>
-        </is>
-      </c>
-      <c r="C365" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D365" s="3" t="inlineStr">
-        <is>
-          <t>[Purbaya Ancam Potong Anggaran Daerah yang Hambat Investasi](https://finance.detik.com/berita-ekonomi-bisnis/d-8550652/purbaya-ancam-potong-anggaran-daerah-yang-hambat-investasi)</t>
-        </is>
-      </c>
-      <c r="E365" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F365" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G365" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B366" s="2" t="inlineStr">
-        <is>
-          <t>20:31</t>
-        </is>
-      </c>
-      <c r="C366" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D366" s="3" t="inlineStr">
-        <is>
-          <t>[Purbaya Mulai Tarik Dana Rp 300 T dari Bank BUMN](https://finance.detik.com/berita-ekonomi-bisnis/d-8546379/purbaya-mulai-tarik-dana-rp-300-t-dari-bank-bumn)</t>
-        </is>
-      </c>
-      <c r="E366" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F366" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G366" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B367" s="2" t="inlineStr">
-        <is>
-          <t>20:31</t>
-        </is>
-      </c>
-      <c r="C367" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D367" s="3" t="inlineStr">
-        <is>
-          <t>[Beras IR. III (IR 64)](https://finance.detik.com/info-pangan/jakarta/beras-ir-iii-ir-64)</t>
-        </is>
-      </c>
-      <c r="E367" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F367" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G367" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B368" s="2" t="inlineStr">
-        <is>
-          <t>20:31</t>
-        </is>
-      </c>
-      <c r="C368" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D368" s="3" t="inlineStr">
-        <is>
-          <t>[Cabe Merah Keriting](https://finance.detik.com/info-pangan/jakarta/cabe-merah-keriting)</t>
-        </is>
-      </c>
-      <c r="E368" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F368" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G368" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B369" s="2" t="inlineStr">
-        <is>
-          <t>20:31</t>
-        </is>
-      </c>
-      <c r="C369" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D369" s="3" t="inlineStr">
-        <is>
-          <t>[Daging Sapi Murni (Semur)](https://finance.detik.com/info-pangan/jakarta/daging-sapi-murni-semur)</t>
-        </is>
-      </c>
-      <c r="E369" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F369" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G369" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B370" s="2" t="inlineStr">
-        <is>
-          <t>20:31</t>
-        </is>
-      </c>
-      <c r="C370" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D370" s="3" t="inlineStr">
-        <is>
-          <t>[Pertamina Kerja Sama dengan Pupuk Indonesia untuk Dukung Ketahanan Pangan](https://finance.detik.com/berita-ekonomi-bisnis/d-8555820/pertamina-kerja-sama-dengan-pupuk-indonesia-untuk-dukung-ketahanan-pangan)</t>
-        </is>
-      </c>
-      <c r="E370" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F370" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G370" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B371" s="2" t="inlineStr">
-        <is>
-          <t>20:31</t>
-        </is>
-      </c>
-      <c r="C371" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D371" s="3" t="inlineStr">
-        <is>
-          <t>[Drone Buatan Bandung Tembus Pasar Australia dan Korea](https://finance.detik.com/foto-bisnis/d-8555166/drone-buatan-bandung-tembus-pasar-australia-dan-korea)</t>
-        </is>
-      </c>
-      <c r="E371" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F371" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G371" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B372" s="2" t="inlineStr">
-        <is>
-          <t>20:31</t>
-        </is>
-      </c>
-      <c r="C372" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D372" s="3" t="inlineStr">
-        <is>
-          <t>[Alasan INA Masih Genggam Saham Bank BUMN Saat Pasar Gonjang-ganjing](https://finance.detik.com/bursa-dan-valas/d-8555623/alasan-ina-masih-genggam-saham-bank-bumn-saat-pasar-gonjang-ganjing)</t>
-        </is>
-      </c>
-      <c r="E372" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F372" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G372" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B373" s="2" t="inlineStr">
-        <is>
-          <t>20:31</t>
-        </is>
-      </c>
-      <c r="C373" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D373" s="3" t="inlineStr">
-        <is>
-          <t>[Toko Online Pungut Pajak Mulai Agustus, Sistem Sudah Siap?](https://finance.detik.com/berita-ekonomi-bisnis/d-8555604/toko-online-pungut-pajak-mulai-agustus-sistem-sudah-siap)</t>
-        </is>
-      </c>
-      <c r="E373" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F373" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G373" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B374" s="2" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="C374" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D374" s="3" t="inlineStr">
-        <is>
-          <t>detikFinance - Berita Ekonomi Bisnis, dan Investasi Hari Ini</t>
-        </is>
-      </c>
-      <c r="E374" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F374" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G374" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B375" s="2" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="C375" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D375" s="3" t="inlineStr">
-        <is>
-          <t>[Prabowo: Jadilah Polisi Dekat Rakyat, Gaji Kita dari Rakyat](https://finance.detik.com/berita-ekonomi-bisnis/d-8554838/prabowo-jadilah-polisi-dekat-rakyat-gaji-kita-dari-rakyat)</t>
-        </is>
-      </c>
-      <c r="E375" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F375" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G375" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B376" s="4" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="C376" s="4" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D376" s="5" t="inlineStr">
-        <is>
-          <t>[Prabowo: Tak Ada Pertumbuhan Ekonomi Tanpa Kepastian Hukum](https://finance.detik.com/berita-ekonomi-bisnis/d-8554797/prabowo-tak-ada-pertumbuhan-ekonomi-tanpa-kepastian-hukum)</t>
-        </is>
-      </c>
-      <c r="E376" s="4" t="inlineStr">
-        <is>
-          <t>POSITIF</t>
-        </is>
-      </c>
-      <c r="F376" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G376" s="4" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B377" s="2" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="C377" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D377" s="3" t="inlineStr">
-        <is>
-          <t>[Bandara Husein Sastranegara Ditargetkan Beroperasi Lagi 17 September](https://finance.detik.com/berita-ekonomi-bisnis/d-8554712/bandara-husein-sastranegara-ditargetkan-beroperasi-lagi-17-september)</t>
-        </is>
-      </c>
-      <c r="E377" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F377" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G377" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B378" s="6" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="C378" s="6" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D378" s="7" t="inlineStr">
-        <is>
-          <t>[Harga BBM Diesel Shell &amp; BP Turun, Ini Daftarnya](https://finance.detik.com/energi/d-8554652/harga-bbm-diesel-shell-bp-turun-ini-daftarnya)</t>
-        </is>
-      </c>
-      <c r="E378" s="6" t="inlineStr">
-        <is>
-          <t>NEGATIF</t>
-        </is>
-      </c>
-      <c r="F378" s="6" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="G378" s="6" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B379" s="6" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="C379" s="6" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D379" s="7" t="inlineStr">
-        <is>
-          <t>[Pertamax Tetap! Ini Daftar BBM Pertamina yang Turun Harga](https://finance.detik.com/energi/d-8554611/pertamax-tetap-ini-daftar-bbm-pertamina-yang-turun-harga)</t>
-        </is>
-      </c>
-      <c r="E379" s="6" t="inlineStr">
-        <is>
-          <t>NEGATIF</t>
-        </is>
-      </c>
-      <c r="F379" s="6" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="G379" s="6" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B380" s="2" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="C380" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D380" s="3" t="inlineStr">
-        <is>
-          <t>[Purbaya Lantik Dirjen Anggaran &amp; Dirjen Kekayaan Baru, Ini Sosoknya](https://finance.detik.com/berita-ekonomi-bisnis/d-8555797/purbaya-lantik-dirjen-anggaran-dirjen-kekayaan-baru-ini-sosoknya)</t>
-        </is>
-      </c>
-      <c r="E380" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F380" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G380" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B381" s="2" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="C381" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D381" s="3" t="inlineStr">
-        <is>
-          <t>[Purbaya Ancam Potong Anggaran Daerah yang Hambat Investasi](https://finance.detik.com/berita-ekonomi-bisnis/d-8550652/purbaya-ancam-potong-anggaran-daerah-yang-hambat-investasi)</t>
-        </is>
-      </c>
-      <c r="E381" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F381" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G381" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B382" s="2" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="C382" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D382" s="3" t="inlineStr">
-        <is>
-          <t>[Purbaya Mulai Tarik Dana Rp 300 T dari Bank BUMN](https://finance.detik.com/berita-ekonomi-bisnis/d-8546379/purbaya-mulai-tarik-dana-rp-300-t-dari-bank-bumn)</t>
-        </is>
-      </c>
-      <c r="E382" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F382" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G382" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B383" s="2" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="C383" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D383" s="3" t="inlineStr">
-        <is>
-          <t>[Beras IR. III (IR 64)](https://finance.detik.com/info-pangan/jakarta/beras-ir-iii-ir-64)</t>
-        </is>
-      </c>
-      <c r="E383" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F383" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G383" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B384" s="2" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="C384" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D384" s="3" t="inlineStr">
-        <is>
-          <t>[Cabe Merah Keriting](https://finance.detik.com/info-pangan/jakarta/cabe-merah-keriting)</t>
-        </is>
-      </c>
-      <c r="E384" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F384" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G384" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B385" s="2" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="C385" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D385" s="3" t="inlineStr">
-        <is>
-          <t>[Daging Sapi Murni (Semur)](https://finance.detik.com/info-pangan/jakarta/daging-sapi-murni-semur)</t>
-        </is>
-      </c>
-      <c r="E385" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F385" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G385" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B386" s="2" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="C386" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D386" s="3" t="inlineStr">
-        <is>
-          <t>[Pertamina Kerja Sama dengan Pupuk Indonesia untuk Dukung Ketahanan Pangan](https://finance.detik.com/berita-ekonomi-bisnis/d-8555820/pertamina-kerja-sama-dengan-pupuk-indonesia-untuk-dukung-ketahanan-pangan)</t>
-        </is>
-      </c>
-      <c r="E386" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F386" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G386" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B387" s="2" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="C387" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D387" s="3" t="inlineStr">
-        <is>
-          <t>[Drone Buatan Bandung Tembus Pasar Australia dan Korea](https://finance.detik.com/foto-bisnis/d-8555166/drone-buatan-bandung-tembus-pasar-australia-dan-korea)</t>
-        </is>
-      </c>
-      <c r="E387" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F387" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G387" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B388" s="2" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="C388" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D388" s="3" t="inlineStr">
-        <is>
-          <t>[Alasan INA Masih Genggam Saham Bank BUMN Saat Pasar Gonjang-ganjing](https://finance.detik.com/bursa-dan-valas/d-8555623/alasan-ina-masih-genggam-saham-bank-bumn-saat-pasar-gonjang-ganjing)</t>
-        </is>
-      </c>
-      <c r="E388" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F388" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G388" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B389" s="2" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="C389" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D389" s="3" t="inlineStr">
-        <is>
-          <t>[Toko Online Pungut Pajak Mulai Agustus, Sistem Sudah Siap?](https://finance.detik.com/berita-ekonomi-bisnis/d-8555604/toko-online-pungut-pajak-mulai-agustus-sistem-sudah-siap)</t>
-        </is>
-      </c>
-      <c r="E389" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F389" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G389" s="2" t="inlineStr">
+      <c r="G317" t="inlineStr">
         <is>
           <t>detik finance</t>
         </is>
@@ -14229,75 +11708,74 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Total Berita</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n">
-        <v>388</v>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="B2" t="n">
+        <v>436</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>🟢 Positif</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>9.3%</t>
+      <c r="B3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>9.2%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>🔴 Negatif</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n">
-        <v>73</v>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>18.8%</t>
+      <c r="B4" t="n">
+        <v>81</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>18.6%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>⚪ Netral</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
-        <v>279</v>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>71.9%</t>
+      <c r="B5" t="n">
+        <v>315</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>72.2%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Rata-rata Skor</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
-        <v>-0.06900000000000001</v>
-      </c>
-      <c r="C6" s="8" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>-0.067</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/sentimen_berita.xlsx
+++ b/data/sentimen_berita.xlsx
@@ -18924,7 +18924,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -18959,7 +18959,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -18994,7 +18994,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -19029,7 +19029,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -19064,7 +19064,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -19099,7 +19099,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -19239,7 +19239,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -19274,7 +19274,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -19309,7 +19309,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -19624,7 +19624,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -19729,7 +19729,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -19799,7 +19799,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -19834,7 +19834,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -19869,7 +19869,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -19974,7 +19974,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1629</v>
+        <v>568</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -19989,11 +19989,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>141</v>
+        <v>56</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>9.9%</t>
         </is>
       </c>
     </row>
@@ -20004,11 +20004,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>240</v>
+        <v>99</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>17.4%</t>
         </is>
       </c>
     </row>
@@ -20019,11 +20019,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1248</v>
+        <v>413</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -20034,7 +20034,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.046</v>
+        <v>-0.056</v>
       </c>
     </row>
   </sheetData>

--- a/data/sentimen_berita.xlsx
+++ b/data/sentimen_berita.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Detail" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Ringkasan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -190,14 +190,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -220,7 +219,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -248,7 +247,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -263,9 +262,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -563,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G691"/>
+  <dimension ref="A1:G644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20990,7 +20989,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -21270,7 +21269,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -21305,7 +21304,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -21340,7 +21339,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -21865,7 +21864,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -21900,7 +21899,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -22005,7 +22004,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -22145,7 +22144,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -22565,7 +22564,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -22670,7 +22669,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -22775,7 +22774,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -22810,7 +22809,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -22915,7 +22914,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -22950,7 +22949,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -22985,7 +22984,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -23020,7 +23019,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -23055,7 +23054,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -23083,1680 +23082,35 @@
       </c>
     </row>
     <row r="644">
-      <c r="A644" s="2" t="inlineStr">
+      <c r="A644" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="B644" s="2" t="inlineStr">
-        <is>
-          <t>23:01</t>
-        </is>
-      </c>
-      <c r="C644" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D644" s="3" t="inlineStr">
-        <is>
-          <t>detikFinance - Berita Ekonomi Bisnis, dan Investasi Hari Ini</t>
-        </is>
-      </c>
-      <c r="E644" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F644" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G644" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="645">
-      <c r="A645" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B645" s="2" t="inlineStr">
-        <is>
-          <t>23:01</t>
-        </is>
-      </c>
-      <c r="C645" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D645" s="3" t="inlineStr">
-        <is>
-          <t>[Bakom Buka Suara soal Pemilihan Komisaris BUMN](https://finance.detik.com/berita-ekonomi-bisnis/d-8560734/bakom-buka-suara-soal-pemilihan-komisaris-bumn)</t>
-        </is>
-      </c>
-      <c r="E645" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F645" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G645" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="646">
-      <c r="A646" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B646" s="2" t="inlineStr">
-        <is>
-          <t>23:01</t>
-        </is>
-      </c>
-      <c r="C646" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D646" s="3" t="inlineStr">
-        <is>
-          <t>[Minyakita Bau Solar Bikin Heboh, Produsen Terancam Sanksi Berat!](https://finance.detik.com/berita-ekonomi-bisnis/d-8560451/minyakita-bau-solar-bikin-heboh-produsen-terancam-sanksi-berat)</t>
-        </is>
-      </c>
-      <c r="E646" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F646" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G646" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="647">
-      <c r="A647" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B647" s="4" t="inlineStr">
-        <is>
-          <t>23:01</t>
-        </is>
-      </c>
-      <c r="C647" s="4" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D647" s="5" t="inlineStr">
-        <is>
-          <t>[Harga Emas Sepekan Naik Rp 25.000/Gram, Jadi Segini Sekarang](https://finance.detik.com/berita-ekonomi-bisnis/d-8560318/harga-emas-sepekan-naik-rp-25-000-gram-jadi-segini-sekarang)</t>
-        </is>
-      </c>
-      <c r="E647" s="4" t="inlineStr">
-        <is>
-          <t>POSITIF</t>
-        </is>
-      </c>
-      <c r="F647" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G647" s="4" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="648">
-      <c r="A648" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B648" s="2" t="inlineStr">
-        <is>
-          <t>23:01</t>
-        </is>
-      </c>
-      <c r="C648" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D648" s="3" t="inlineStr">
-        <is>
-          <t>[Daftar 10 Negara yang Warganya Jajal Whoosh Saat ke Indonesia](https://finance.detik.com/infrastruktur/d-8560142/daftar-10-negara-yang-warganya-jajal-whoosh-saat-ke-indonesia)</t>
-        </is>
-      </c>
-      <c r="E648" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F648" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G648" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="649">
-      <c r="A649" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B649" s="6" t="inlineStr">
-        <is>
-          <t>23:01</t>
-        </is>
-      </c>
-      <c r="C649" s="6" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D649" s="7" t="inlineStr">
-        <is>
-          <t>[Nasib Tokopedia Usai Diterjang Badai PHK](https://finance.detik.com/berita-ekonomi-bisnis/d-8560133/nasib-tokopedia-usai-diterjang-badai-phk)</t>
-        </is>
-      </c>
-      <c r="E649" s="6" t="inlineStr">
-        <is>
-          <t>NEGATIF</t>
-        </is>
-      </c>
-      <c r="F649" s="6" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="G649" s="6" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="650">
-      <c r="A650" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B650" s="2" t="inlineStr">
-        <is>
-          <t>23:01</t>
-        </is>
-      </c>
-      <c r="C650" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D650" s="3" t="inlineStr">
-        <is>
-          <t>[Kementan Guyur Rp 1,33 Triliun buat Jadikan Papua Selatan Lumpung Pangan](https://finance.detik.com/berita-ekonomi-bisnis/d-8560966/kementan-guyur-rp-1-33-triliun-buat-jadikan-papua-selatan-lumpung-pangan)</t>
-        </is>
-      </c>
-      <c r="E650" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F650" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G650" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="651">
-      <c r="A651" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B651" s="2" t="inlineStr">
-        <is>
-          <t>23:01</t>
-        </is>
-      </c>
-      <c r="C651" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D651" s="3" t="inlineStr">
-        <is>
-          <t>[Mentan Buka-bukaan Jurus Hadapi Ancaman El Nino](https://finance.detik.com/berita-ekonomi-bisnis/d-8558016/mentan-buka-bukaan-jurus-hadapi-ancaman-el-nino)</t>
-        </is>
-      </c>
-      <c r="E651" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F651" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G651" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="652">
-      <c r="A652" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B652" s="4" t="inlineStr">
-        <is>
-          <t>23:01</t>
-        </is>
-      </c>
-      <c r="C652" s="4" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D652" s="5" t="inlineStr">
-        <is>
-          <t>[Harga Ayam Hidup Didorong Naik Jadi Rp 19.500/Kg Mulai 15 Juli](https://finance.detik.com/berita-ekonomi-bisnis/d-8554561/harga-ayam-hidup-didorong-naik-jadi-rp-19-500-kg-mulai-15-juli)</t>
-        </is>
-      </c>
-      <c r="E652" s="4" t="inlineStr">
-        <is>
-          <t>POSITIF</t>
-        </is>
-      </c>
-      <c r="F652" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G652" s="4" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="653">
-      <c r="A653" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B653" s="2" t="inlineStr">
-        <is>
-          <t>23:01</t>
-        </is>
-      </c>
-      <c r="C653" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D653" s="3" t="inlineStr">
-        <is>
-          <t>[Beras IR. III (IR 64)](https://finance.detik.com/info-pangan/jakarta/beras-ir-iii-ir-64)</t>
-        </is>
-      </c>
-      <c r="E653" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F653" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G653" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="654">
-      <c r="A654" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B654" s="2" t="inlineStr">
-        <is>
-          <t>23:01</t>
-        </is>
-      </c>
-      <c r="C654" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D654" s="3" t="inlineStr">
-        <is>
-          <t>[Cabe Merah Keriting](https://finance.detik.com/info-pangan/jakarta/cabe-merah-keriting)</t>
-        </is>
-      </c>
-      <c r="E654" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F654" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G654" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="655">
-      <c r="A655" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B655" s="2" t="inlineStr">
-        <is>
-          <t>23:01</t>
-        </is>
-      </c>
-      <c r="C655" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D655" s="3" t="inlineStr">
-        <is>
-          <t>[Daging Sapi Murni (Semur)](https://finance.detik.com/info-pangan/jakarta/daging-sapi-murni-semur)</t>
-        </is>
-      </c>
-      <c r="E655" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F655" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G655" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="656">
-      <c r="A656" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B656" s="4" t="inlineStr">
-        <is>
-          <t>23:01</t>
-        </is>
-      </c>
-      <c r="C656" s="4" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D656" s="5" t="inlineStr">
-        <is>
-          <t>[Turis Asing Diam-diam Doyan Naik Kereta di RI, Begini Datanya](https://finance.detik.com/berita-ekonomi-bisnis/d-8560937/turis-asing-diam-diam-doyan-naik-kereta-di-ri-begini-datanya)</t>
-        </is>
-      </c>
-      <c r="E656" s="4" t="inlineStr">
-        <is>
-          <t>POSITIF</t>
-        </is>
-      </c>
-      <c r="F656" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G656" s="4" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="657">
-      <c r="A657" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B657" s="6" t="inlineStr">
-        <is>
-          <t>23:01</t>
-        </is>
-      </c>
-      <c r="C657" s="6" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D657" s="7" t="inlineStr">
-        <is>
-          <t>[Otorita Ungkap Dampak Pembangunan IKN ke Ekonomi](https://finance.detik.com/infrastruktur/d-8560939/otorita-ungkap-dampak-pembangunan-ikn-ke-ekonomi)</t>
-        </is>
-      </c>
-      <c r="E657" s="6" t="inlineStr">
-        <is>
-          <t>NEGATIF</t>
-        </is>
-      </c>
-      <c r="F657" s="6" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="G657" s="6" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="658">
-      <c r="A658" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B658" s="4" t="inlineStr">
-        <is>
-          <t>23:01</t>
-        </is>
-      </c>
-      <c r="C658" s="4" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D658" s="5" t="inlineStr">
-        <is>
-          <t>[258 Juta Orang Naik Kereta dalam 6 Bulan](https://finance.detik.com/berita-ekonomi-bisnis/d-8560932/258-juta-orang-naik-kereta-dalam-6-bulan)</t>
-        </is>
-      </c>
-      <c r="E658" s="4" t="inlineStr">
-        <is>
-          <t>POSITIF</t>
-        </is>
-      </c>
-      <c r="F658" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G658" s="4" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="659">
-      <c r="A659" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B659" s="2" t="inlineStr">
-        <is>
-          <t>23:01</t>
-        </is>
-      </c>
-      <c r="C659" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D659" s="3" t="inlineStr">
-        <is>
-          <t>[Puan soal Pemilihan Komisaris BUMN: Kami Dorong Profesional &amp; Kompeten](https://finance.detik.com/berita-ekonomi-bisnis/d-8560783/puan-soal-pemilihan-komisaris-bumn-kami-dorong-profesional-kompeten)</t>
-        </is>
-      </c>
-      <c r="E659" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F659" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G659" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="660">
-      <c r="A660" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B660" s="2" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
-      <c r="C660" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D660" s="3" t="inlineStr">
-        <is>
-          <t>detikFinance - Berita Ekonomi Bisnis, dan Investasi Hari Ini</t>
-        </is>
-      </c>
-      <c r="E660" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F660" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G660" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="661">
-      <c r="A661" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B661" s="2" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
-      <c r="C661" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D661" s="3" t="inlineStr">
-        <is>
-          <t>[Bakom Buka Suara soal Pemilihan Komisaris BUMN](https://finance.detik.com/berita-ekonomi-bisnis/d-8560734/bakom-buka-suara-soal-pemilihan-komisaris-bumn)</t>
-        </is>
-      </c>
-      <c r="E661" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F661" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G661" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="662">
-      <c r="A662" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B662" s="2" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
-      <c r="C662" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D662" s="3" t="inlineStr">
-        <is>
-          <t>[Minyakita Bau Solar Bikin Heboh, Produsen Terancam Sanksi Berat!](https://finance.detik.com/berita-ekonomi-bisnis/d-8560451/minyakita-bau-solar-bikin-heboh-produsen-terancam-sanksi-berat)</t>
-        </is>
-      </c>
-      <c r="E662" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F662" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G662" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="663">
-      <c r="A663" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B663" s="4" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
-      <c r="C663" s="4" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D663" s="5" t="inlineStr">
-        <is>
-          <t>[Harga Emas Sepekan Naik Rp 25.000/Gram, Jadi Segini Sekarang](https://finance.detik.com/berita-ekonomi-bisnis/d-8560318/harga-emas-sepekan-naik-rp-25-000-gram-jadi-segini-sekarang)</t>
-        </is>
-      </c>
-      <c r="E663" s="4" t="inlineStr">
-        <is>
-          <t>POSITIF</t>
-        </is>
-      </c>
-      <c r="F663" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G663" s="4" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="664">
-      <c r="A664" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B664" s="2" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
-      <c r="C664" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D664" s="3" t="inlineStr">
-        <is>
-          <t>[Daftar 10 Negara yang Warganya Jajal Whoosh Saat ke Indonesia](https://finance.detik.com/infrastruktur/d-8560142/daftar-10-negara-yang-warganya-jajal-whoosh-saat-ke-indonesia)</t>
-        </is>
-      </c>
-      <c r="E664" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F664" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G664" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="665">
-      <c r="A665" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B665" s="6" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
-      <c r="C665" s="6" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D665" s="7" t="inlineStr">
-        <is>
-          <t>[Nasib Tokopedia Usai Diterjang Badai PHK](https://finance.detik.com/berita-ekonomi-bisnis/d-8560133/nasib-tokopedia-usai-diterjang-badai-phk)</t>
-        </is>
-      </c>
-      <c r="E665" s="6" t="inlineStr">
-        <is>
-          <t>NEGATIF</t>
-        </is>
-      </c>
-      <c r="F665" s="6" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="G665" s="6" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="666">
-      <c r="A666" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B666" s="2" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
-      <c r="C666" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D666" s="3" t="inlineStr">
-        <is>
-          <t>[Kementan Guyur Rp 1,33 Triliun buat Jadikan Papua Selatan Lumpung Pangan](https://finance.detik.com/berita-ekonomi-bisnis/d-8560966/kementan-guyur-rp-1-33-triliun-buat-jadikan-papua-selatan-lumpung-pangan)</t>
-        </is>
-      </c>
-      <c r="E666" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F666" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G666" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="667">
-      <c r="A667" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B667" s="2" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
-      <c r="C667" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D667" s="3" t="inlineStr">
-        <is>
-          <t>[Mentan Buka-bukaan Jurus Hadapi Ancaman El Nino](https://finance.detik.com/berita-ekonomi-bisnis/d-8558016/mentan-buka-bukaan-jurus-hadapi-ancaman-el-nino)</t>
-        </is>
-      </c>
-      <c r="E667" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F667" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G667" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="668">
-      <c r="A668" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B668" s="4" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
-      <c r="C668" s="4" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D668" s="5" t="inlineStr">
-        <is>
-          <t>[Harga Ayam Hidup Didorong Naik Jadi Rp 19.500/Kg Mulai 15 Juli](https://finance.detik.com/berita-ekonomi-bisnis/d-8554561/harga-ayam-hidup-didorong-naik-jadi-rp-19-500-kg-mulai-15-juli)</t>
-        </is>
-      </c>
-      <c r="E668" s="4" t="inlineStr">
-        <is>
-          <t>POSITIF</t>
-        </is>
-      </c>
-      <c r="F668" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G668" s="4" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="669">
-      <c r="A669" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B669" s="2" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
-      <c r="C669" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D669" s="3" t="inlineStr">
-        <is>
-          <t>[Beras IR. III (IR 64)](https://finance.detik.com/info-pangan/jakarta/beras-ir-iii-ir-64)</t>
-        </is>
-      </c>
-      <c r="E669" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F669" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G669" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="670">
-      <c r="A670" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B670" s="2" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
-      <c r="C670" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D670" s="3" t="inlineStr">
-        <is>
-          <t>[Cabe Merah Keriting](https://finance.detik.com/info-pangan/jakarta/cabe-merah-keriting)</t>
-        </is>
-      </c>
-      <c r="E670" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F670" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G670" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="671">
-      <c r="A671" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B671" s="2" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
-      <c r="C671" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D671" s="3" t="inlineStr">
-        <is>
-          <t>[Daging Sapi Murni (Semur)](https://finance.detik.com/info-pangan/jakarta/daging-sapi-murni-semur)</t>
-        </is>
-      </c>
-      <c r="E671" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F671" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G671" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="672">
-      <c r="A672" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B672" s="4" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
-      <c r="C672" s="4" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D672" s="5" t="inlineStr">
-        <is>
-          <t>[Turis Asing Diam-diam Doyan Naik Kereta di RI, Begini Datanya](https://finance.detik.com/berita-ekonomi-bisnis/d-8560937/turis-asing-diam-diam-doyan-naik-kereta-di-ri-begini-datanya)</t>
-        </is>
-      </c>
-      <c r="E672" s="4" t="inlineStr">
-        <is>
-          <t>POSITIF</t>
-        </is>
-      </c>
-      <c r="F672" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G672" s="4" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="673">
-      <c r="A673" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B673" s="6" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
-      <c r="C673" s="6" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D673" s="7" t="inlineStr">
-        <is>
-          <t>[Otorita Ungkap Dampak Pembangunan IKN ke Ekonomi](https://finance.detik.com/infrastruktur/d-8560939/otorita-ungkap-dampak-pembangunan-ikn-ke-ekonomi)</t>
-        </is>
-      </c>
-      <c r="E673" s="6" t="inlineStr">
-        <is>
-          <t>NEGATIF</t>
-        </is>
-      </c>
-      <c r="F673" s="6" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="G673" s="6" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="674">
-      <c r="A674" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B674" s="4" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
-      <c r="C674" s="4" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D674" s="5" t="inlineStr">
-        <is>
-          <t>[258 Juta Orang Naik Kereta dalam 6 Bulan](https://finance.detik.com/berita-ekonomi-bisnis/d-8560932/258-juta-orang-naik-kereta-dalam-6-bulan)</t>
-        </is>
-      </c>
-      <c r="E674" s="4" t="inlineStr">
-        <is>
-          <t>POSITIF</t>
-        </is>
-      </c>
-      <c r="F674" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G674" s="4" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="675">
-      <c r="A675" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B675" s="2" t="inlineStr">
-        <is>
-          <t>23:15</t>
-        </is>
-      </c>
-      <c r="C675" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D675" s="3" t="inlineStr">
-        <is>
-          <t>[Puan soal Pemilihan Komisaris BUMN: Kami Dorong Profesional &amp; Kompeten](https://finance.detik.com/berita-ekonomi-bisnis/d-8560783/puan-soal-pemilihan-komisaris-bumn-kami-dorong-profesional-kompeten)</t>
-        </is>
-      </c>
-      <c r="E675" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F675" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G675" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="676">
-      <c r="A676" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B676" s="2" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C676" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D676" s="3" t="inlineStr">
-        <is>
-          <t>detikFinance - Berita Ekonomi Bisnis, dan Investasi Hari Ini</t>
-        </is>
-      </c>
-      <c r="E676" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F676" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G676" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="677">
-      <c r="A677" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B677" s="2" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C677" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D677" s="3" t="inlineStr">
-        <is>
-          <t>[Bakom Buka Suara soal Pemilihan Komisaris BUMN](https://finance.detik.com/berita-ekonomi-bisnis/d-8560734/bakom-buka-suara-soal-pemilihan-komisaris-bumn)</t>
-        </is>
-      </c>
-      <c r="E677" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F677" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G677" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="678">
-      <c r="A678" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B678" s="2" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C678" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D678" s="3" t="inlineStr">
-        <is>
-          <t>[Minyakita Bau Solar Bikin Heboh, Produsen Terancam Sanksi Berat!](https://finance.detik.com/berita-ekonomi-bisnis/d-8560451/minyakita-bau-solar-bikin-heboh-produsen-terancam-sanksi-berat)</t>
-        </is>
-      </c>
-      <c r="E678" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F678" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G678" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="679">
-      <c r="A679" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B679" s="4" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C679" s="4" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D679" s="5" t="inlineStr">
-        <is>
-          <t>[Harga Emas Sepekan Naik Rp 25.000/Gram, Jadi Segini Sekarang](https://finance.detik.com/berita-ekonomi-bisnis/d-8560318/harga-emas-sepekan-naik-rp-25-000-gram-jadi-segini-sekarang)</t>
-        </is>
-      </c>
-      <c r="E679" s="4" t="inlineStr">
-        <is>
-          <t>POSITIF</t>
-        </is>
-      </c>
-      <c r="F679" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G679" s="4" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="680">
-      <c r="A680" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B680" s="2" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C680" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D680" s="3" t="inlineStr">
-        <is>
-          <t>[Daftar 10 Negara yang Warganya Jajal Whoosh Saat ke Indonesia](https://finance.detik.com/infrastruktur/d-8560142/daftar-10-negara-yang-warganya-jajal-whoosh-saat-ke-indonesia)</t>
-        </is>
-      </c>
-      <c r="E680" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F680" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G680" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="681">
-      <c r="A681" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B681" s="6" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C681" s="6" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D681" s="7" t="inlineStr">
-        <is>
-          <t>[Nasib Tokopedia Usai Diterjang Badai PHK](https://finance.detik.com/berita-ekonomi-bisnis/d-8560133/nasib-tokopedia-usai-diterjang-badai-phk)</t>
-        </is>
-      </c>
-      <c r="E681" s="6" t="inlineStr">
-        <is>
-          <t>NEGATIF</t>
-        </is>
-      </c>
-      <c r="F681" s="6" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="G681" s="6" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="682">
-      <c r="A682" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B682" s="2" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C682" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D682" s="3" t="inlineStr">
-        <is>
-          <t>[Kementan Guyur Rp 1,33 Triliun buat Jadikan Papua Selatan Lumpung Pangan](https://finance.detik.com/berita-ekonomi-bisnis/d-8560966/kementan-guyur-rp-1-33-triliun-buat-jadikan-papua-selatan-lumpung-pangan)</t>
-        </is>
-      </c>
-      <c r="E682" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F682" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G682" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="683">
-      <c r="A683" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B683" s="2" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C683" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D683" s="3" t="inlineStr">
-        <is>
-          <t>[Mentan Buka-bukaan Jurus Hadapi Ancaman El Nino](https://finance.detik.com/berita-ekonomi-bisnis/d-8558016/mentan-buka-bukaan-jurus-hadapi-ancaman-el-nino)</t>
-        </is>
-      </c>
-      <c r="E683" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F683" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G683" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="684">
-      <c r="A684" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B684" s="4" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C684" s="4" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D684" s="5" t="inlineStr">
-        <is>
-          <t>[Harga Ayam Hidup Didorong Naik Jadi Rp 19.500/Kg Mulai 15 Juli](https://finance.detik.com/berita-ekonomi-bisnis/d-8554561/harga-ayam-hidup-didorong-naik-jadi-rp-19-500-kg-mulai-15-juli)</t>
-        </is>
-      </c>
-      <c r="E684" s="4" t="inlineStr">
-        <is>
-          <t>POSITIF</t>
-        </is>
-      </c>
-      <c r="F684" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G684" s="4" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="685">
-      <c r="A685" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B685" s="2" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C685" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D685" s="3" t="inlineStr">
-        <is>
-          <t>[Beras IR. III (IR 64)](https://finance.detik.com/info-pangan/jakarta/beras-ir-iii-ir-64)</t>
-        </is>
-      </c>
-      <c r="E685" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F685" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G685" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="686">
-      <c r="A686" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B686" s="2" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C686" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D686" s="3" t="inlineStr">
-        <is>
-          <t>[Cabe Merah Keriting](https://finance.detik.com/info-pangan/jakarta/cabe-merah-keriting)</t>
-        </is>
-      </c>
-      <c r="E686" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F686" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G686" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="687">
-      <c r="A687" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B687" s="2" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C687" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D687" s="3" t="inlineStr">
-        <is>
-          <t>[Daging Sapi Murni (Semur)](https://finance.detik.com/info-pangan/jakarta/daging-sapi-murni-semur)</t>
-        </is>
-      </c>
-      <c r="E687" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F687" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G687" s="2" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="688">
-      <c r="A688" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B688" s="4" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C688" s="4" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D688" s="5" t="inlineStr">
-        <is>
-          <t>[Turis Asing Diam-diam Doyan Naik Kereta di RI, Begini Datanya](https://finance.detik.com/berita-ekonomi-bisnis/d-8560937/turis-asing-diam-diam-doyan-naik-kereta-di-ri-begini-datanya)</t>
-        </is>
-      </c>
-      <c r="E688" s="4" t="inlineStr">
-        <is>
-          <t>POSITIF</t>
-        </is>
-      </c>
-      <c r="F688" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G688" s="4" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="689">
-      <c r="A689" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B689" s="6" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C689" s="6" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D689" s="7" t="inlineStr">
-        <is>
-          <t>[Otorita Ungkap Dampak Pembangunan IKN ke Ekonomi](https://finance.detik.com/infrastruktur/d-8560939/otorita-ungkap-dampak-pembangunan-ikn-ke-ekonomi)</t>
-        </is>
-      </c>
-      <c r="E689" s="6" t="inlineStr">
-        <is>
-          <t>NEGATIF</t>
-        </is>
-      </c>
-      <c r="F689" s="6" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="G689" s="6" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="690">
-      <c r="A690" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B690" s="4" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C690" s="4" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D690" s="5" t="inlineStr">
-        <is>
-          <t>[258 Juta Orang Naik Kereta dalam 6 Bulan](https://finance.detik.com/berita-ekonomi-bisnis/d-8560932/258-juta-orang-naik-kereta-dalam-6-bulan)</t>
-        </is>
-      </c>
-      <c r="E690" s="4" t="inlineStr">
-        <is>
-          <t>POSITIF</t>
-        </is>
-      </c>
-      <c r="F690" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G690" s="4" t="inlineStr">
-        <is>
-          <t>detik finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="691">
-      <c r="A691" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B691" s="2" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C691" s="2" t="inlineStr">
-        <is>
-          <t>berita ekonomi</t>
-        </is>
-      </c>
-      <c r="D691" s="3" t="inlineStr">
-        <is>
-          <t>[Puan soal Pemilihan Komisaris BUMN: Kami Dorong Profesional &amp; Kompeten](https://finance.detik.com/berita-ekonomi-bisnis/d-8560783/puan-soal-pemilihan-komisaris-bumn-kami-dorong-profesional-kompeten)</t>
-        </is>
-      </c>
-      <c r="E691" s="2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F691" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G691" s="2" t="inlineStr">
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>23:46</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>berita ekonomi</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>[Penasihat Khusus Presiden Bicara Nasib PT Granito, Singgung Danantara](https://finance.detik.com/berita-ekonomi-bisnis/d-8555948/penasihat-khusus-presiden-bicara-nasib-pt-granito-singgung-danantara)</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>NETRAL</t>
+        </is>
+      </c>
+      <c r="F644" t="n">
+        <v>0</v>
+      </c>
+      <c r="G644" t="inlineStr">
         <is>
           <t>detik finance</t>
         </is>
@@ -24799,75 +23153,74 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Total Berita</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n">
-        <v>690</v>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="B2" t="n">
+        <v>706</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>🟢 Positif</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
-        <v>85</v>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>12.3%</t>
+      <c r="B3" t="n">
+        <v>89</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12.6%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>🔴 Negatif</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n">
-        <v>113</v>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>16.4%</t>
+      <c r="B4" t="n">
+        <v>115</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>16.3%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>⚪ Netral</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
-        <v>492</v>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>71.3%</t>
+      <c r="B5" t="n">
+        <v>502</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>71.1%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Rata-rata Skor</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
-        <v>-0.032</v>
-      </c>
-      <c r="C6" s="8" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>-0.03</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
